--- a/data_extactor/batch/851_900.xlsx
+++ b/data_extactor/batch/851_900.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEC1116-6788-498B-89E4-71293570FB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,1600 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="529">
+  <si>
+    <t>51-4032.00</t>
+  </si>
+  <si>
+    <t>Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Bore Mill Operator | CNC Drilling Operator (Computer Numerical Control Drilling Operator) | CNC Machinist (Computer Numerical Control Machinist) | Drill Operator | Drill Press Operator | Drill Setup Operator | Machine Operator | Punch Operator | Radial Drill Operator | Setup Mill Operator</t>
+  </si>
+  <si>
+    <t>Automated inventory software | Computerized numerical control CNC software | Microsoft Excel | Microsoft Office software | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Mathematics | Production and Processing | Mechanical | English Language | Engineering and Technology | Education and Training | Design | Administration and Management</t>
+  </si>
+  <si>
+    <t>Control Precision | Near Vision | Arm-Hand Steadiness | Problem Sensitivity | Information Ordering | Selective Attention | Manual Dexterity | Finger Dexterity | Reaction Time | Rate Control | Visualization | Written Comprehension | Oral Comprehension | Perceptual Speed | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Written Expression | Oral Expression | Far Vision</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Contact With Others | Freedom to Make Decisions | Exposed to Hazardous Equipment | Determine Tasks, Priorities and Goals | Spend Time Standing | Impact of Decisions on Co-workers or Company Results | Pace Determined by Speed of Equipment | Indoors, Environmentally Controlled | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Consequence of Error | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Computer Numerically Controlled Tool Operators | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Earth Drillers, Except Oil and Gas | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Layout Workers, Metal and Plastic | Machinists | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sawing Machine Setters, Operators, and Tenders, Wood | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend drilling machines to drill, bore, ream, mill, or countersink metal or plastic work pieces.</t>
+  </si>
+  <si>
+    <t>Change worn cutting tools, using wrenches. | Establish zero reference points on workpieces, such as at the intersections of two edges or over hole locations. | Install tools in spindles. | Lay out reference lines and machining locations on work, using layout tools, and applying knowledge of shop math and layout techniques. | Lift workpieces onto work tables either manually or with hoists or direct crane operators to lift and position workpieces. | Move machine controls to lower tools to workpieces and to engage automatic feeds. | Observe drilling or boring machine operations to detect any problems. | Operate single- or multiple-spindle drill presses to bore holes so that machining operations can be performed on metal or plastic workpieces. | Operate tracing attachments to duplicate contours from templates or models. | Perform minor assembly, such as fastening parts with nuts, bolts, or screws, using power tools or hand tools. | Position and secure workpieces on tables, using bolts, jigs, clamps, shims, or other holding devices. | Select and set cutting speeds, feed rates, depths of cuts, and cutting tools, according to machining instructions or knowledge of metal properties. | Sharpen cutting tools, using bench grinders. | Study machining instructions, job orders, or blueprints to determine dimensional or finish specifications, sequences of operations, setups, or tooling requirements. | Turn valves and direct flow of coolants or cutting oil over cutting areas. | Verify conformance of machined work to specifications, using measuring instruments, such as calipers, micrometers, or fixed or telescoping gauges. | Verify that workpiece reference lines are parallel to the axis of table rotation, using dial indicators mounted in spindles.</t>
+  </si>
+  <si>
+    <t>51-4033.00</t>
+  </si>
+  <si>
+    <t>Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Cell Operator | Centerless Grinder Operator | Deburrer | Die Maintenance Technician | Finisher | Grinder | Grinder Operator | Grinding Machine Operator | Process Equipment Operator</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Manufacturing reporting system | Mazak Mazatrol SMART CNC | Microsoft Excel | Microsoft Office software | Microsoft Windows | SAP software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing</t>
+  </si>
+  <si>
+    <t>Control Precision | Manual Dexterity | Near Vision | Problem Sensitivity | Reaction Time | Multilimb Coordination | Arm-Hand Steadiness | Perceptual Speed | Rate Control | Depth Perception | Far Vision | Trunk Strength | Static Strength | Finger Dexterity | Selective Attention | Visualization | Flexibility of Closure | Information Ordering | Deductive Reasoning | Written Comprehension | Inductive Reasoning | Oral Expression | Oral Comprehension | Auditory Attention | Wrist-Finger Speed</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Time Pressure | Indoors, Environmentally Controlled | Spend Time Standing | Pace Determined by Speed of Equipment | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Hazardous Equipment | Impact of Decisions on Co-workers or Company Results | Spend Time Making Repetitive Motions | Exposed to Contaminants | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sawing Machine Setters, Operators, and Tenders, Wood | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend grinding and related tools that remove excess material or burrs from surfaces, sharpen edges or corners, or buff, hone, or polish metal or plastic work pieces.</t>
+  </si>
+  <si>
+    <t>Activate machine start-up switches to grind, lap, hone, debar, shear, or cut workpieces, according to specifications. | Adjust air cylinders and setting stops to set traverse lengths and feed arm strokes. | Brush or spray lubricating compounds on workpieces, or turn valve handles and direct flow of coolant against tools and workpieces. | Compute machine indexings and settings for specified dimensions and base reference points. | Inspect or measure finished workpieces to determine conformance to specifications, using measuring instruments, such as gauges or micrometers. | Lift and position workpieces, manually or with hoists, and secure them in hoppers or on machine tables, faceplates, or chucks, using clamps. | Maintain stocks of machine parts and machining tools. | Measure workpieces and lay out work, using precision measuring devices. | Mount and position tools in machine chucks, spindles, or other tool holding devices, using hand tools. | Move machine controls to index workpieces, and to adjust machines for pre-selected operational settings. | Observe machine operations to detect any problems, making necessary adjustments to correct problems. | Repair or replace machine parts, using hand tools, or notify engineering personnel when corrective action is required. | Select machine tooling to be used, using knowledge of machine and production requirements. | Set and adjust machine controls according to product specifications, using knowledge of machine operation. | Set up, operate, or tend grinding and related tools that remove excess material or burrs from surfaces, sharpen edges or corners, or buff, hone, or polish metal or plastic workpieces. | Slide spacers between buffs on spindles to set spacing. | Study blueprints, work orders, or machining instructions to determine product specifications, tool requirements, and operational sequences. | Thread and hand-feed materials through machine cutters or abraders.</t>
+  </si>
+  <si>
+    <t>51-4034.00</t>
+  </si>
+  <si>
+    <t>Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>CNC Lathe Operator (Computer Numerical Control Lathe Operator) | CNC Setup Operator (Computer Numerical Control Setup Operator) | Lathe Operator | Machine Operator | Numerical Control Operator (NC Operator) | Screw Machine Operator | Screw Machine Tool Setter | Setup Operator | Turn Operator</t>
+  </si>
+  <si>
+    <t>Autodesk HSMWorks | Computer numerical control CNC editor software | G-code | Inventory tracking software | M-code</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Engineering and Technology | Education and Training | Administration and Management | Customer and Personal Service | English Language | Mathematics</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Control Precision | Near Vision | Finger Dexterity | Reaction Time | Rate Control | Multilimb Coordination | Manual Dexterity | Visualization | Problem Sensitivity | Oral Comprehension | Trunk Strength | Selective Attention | Perceptual Speed | Information Ordering | Deductive Reasoning | Oral Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Indoors, Environmentally Controlled | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Coil Winders, Tapers, and Finishers | Computer Numerically Controlled Tool Operators | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Machine Feeders and Offbearers | Machinists | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend lathe and turning machines to turn, bore, thread, form, or face metal or plastic materials, such as wire, rod, or bar stock.</t>
+  </si>
+  <si>
+    <t>Adjust machine controls and change tool settings to keep dimensions within specified tolerances. | Clean work area. | Compute unspecified dimensions and machine settings, using knowledge of metal properties and shop mathematics. | Crank machines through cycles, stopping to adjust tool positions and machine controls to ensure specified timing, clearances, and tolerances. | Inspect sample workpieces to verify conformance with specifications, using instruments such as gauges, micrometers, and dial indicators. | Install holding fixtures, cams, gears, and stops to control stock and tool movement, using hand tools, power tools, and measuring instruments. | Lift metal stock or workpieces manually or using hoists, and position and secure them in machines, using fasteners and hand tools. | Mount attachments, such as relieving or tracing attachments, to perform operations, such as duplicating contours of templates or trimming workpieces. | Move controls to set cutting speeds and depths and feed rates, and to position tools in relation to workpieces. | Move toolholders manually or by turning handwheels, or engage automatic feeding mechanisms to feed tools to and along workpieces. | Position, secure, and align cutting tools in toolholders on machines, using hand tools, and verify their positions with measuring instruments. | Program computer numerical control machines. | Refill, change, and monitor the level of fluids, such as oil and coolant, in machines. | Replace worn tools, and sharpen dull cutting tools and dies, using bench grinders or cutter-grinding machines. | Select cutting tools and tooling instructions, according to written specifications or knowledge of metal properties and shop mathematics. | Start lathe or turning machines and observe operations to ensure that specifications are met. | Study blueprints, layouts or charts, and job orders for information on specifications and tooling instructions, and to determine material requirements and operational sequences. | Turn valve handles to direct the flow of coolant onto work areas or to coat disks with spinning compounds.</t>
+  </si>
+  <si>
+    <t>51-4035.00</t>
+  </si>
+  <si>
+    <t>Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>CNC Licensed Mill Operator (Computer Numerical Control Licensed Mill Operator) | CNC Mill Operator (Computer Numerical Control Mill Operator) | CNC Mill Operator (Computerized Numerical Control Mill Operator) | CNC Mill Set Up Operator (Computerized Numerical Control Mill Set Up Operator) | Machine Operator | Machine Set Up Operator | Mill Operator | Miller | Milling Operator | Setup Man</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | EditCNC | Extensible markup language XML | G-code | Kentech machine shop software | M-code | Mastercam computer-aided design and manufacturing software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | SWIVEL Software | Siemens Solid Edge | SmartCAMcnc SmartCAM | Vero Software ALPHACAM | Vero Software Edgecam</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Production and Processing | English Language | Mathematics | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Near Vision | Control Precision | Arm-Hand Steadiness | Problem Sensitivity | Multilimb Coordination | Reaction Time | Trunk Strength | Finger Dexterity | Selective Attention | Visualization | Information Ordering | Deductive Reasoning | Oral Comprehension | Written Comprehension | Speech Recognition | Inductive Reasoning | Oral Expression</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Time Pressure | Pace Determined by Speed of Equipment | Spend Time Walking or Running | Spend Time Making Repetitive Motions | Indoors, Not Environmentally Controlled | Exposed to Hazardous Equipment | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Computer Numerically Controlled Tool Operators | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Machinists | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sawing Machine Setters, Operators, and Tenders, Wood | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend milling or planing machines to mill, plane, shape, groove, or profile metal or plastic work pieces.</t>
+  </si>
+  <si>
+    <t>Compute dimensions, tolerances, and angles of workpieces or machines according to specifications and knowledge of metal properties and shop mathematics. | Make templates or cutting tools. | Mount attachments and tools, such as pantographs, engravers, or routers, to perform other operations, such as drilling or boring. | Move controls to set cutting specifications, to position cutting tools and workpieces in relation to each other, and to start machines. | Move cutters or material manually or by turning handwheels, or engage automatic feeding mechanisms to mill workpieces to specifications. | Observe milling or planing machine operation, and adjust controls to ensure conformance with specified tolerances. | Position and secure workpieces on machines, using holding devices, measuring instruments, hand tools, and hoists. | Record production output. | Remove workpieces from machines, and check to ensure that they conform to specifications, using measuring instruments such as microscopes, gauges, calipers, and micrometers. | Replace worn tools, using hand tools, and sharpen dull tools, using bench grinders. | Select and install cutting tools and other accessories according to specifications, using hand tools or power tools. | Select cutting speeds, feed rates, and depths of cuts, applying knowledge of metal properties and shop mathematics. | Study blueprints, layouts, sketches, or work orders to assess workpiece specifications and to determine tooling instructions, tools and materials needed, and sequences of operations. | Turn valves or pull levers to start and regulate the flow of coolant or lubricant to work areas. | Verify alignment of workpieces on machines, using measuring instruments such as rules, gauges, or calipers.</t>
+  </si>
+  <si>
+    <t>51-4041.00</t>
+  </si>
+  <si>
+    <t>Machinists</t>
+  </si>
+  <si>
+    <t>CNC Machinist (Computer Numeric Controlled Machinist) | CNC Machinist (Computer Numerically Controlled Machinist) | Gear Machinist | Machine Repair Person | Machinist | Maintenance Machinist | Manual Lathe Machinist | Production Machinist | Tool Room Machinist</t>
+  </si>
+  <si>
+    <t>3D Printing software | Armchair Machinist software | Autodesk AutoCAD | Autodesk Fusion 360 | Autodesk HSMWorks | CNC Consulting Machinists' Calculator | CNC Mastercam | Dassault Systemes CATIA | Dassault Systemes SolidWorks | ERP software | EditCNC | G-code | GRZ Software MeshCAM | Hexagon Metrology PC-DMIS | IMSI TurboCAD | JETCAM | JobBOSS | Kentech Kipware Studio | Kentech Kipware Trig Kalculator | Mastercam computer-aided design and manufacturing software | Mazak Mazatrol SMART CNC | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | OnShape | OneCNC CAD/CAM | PTC Creo Parametric | SAP software | Siemens NX | SolidCAM CAM software | Vero Software SURFCAM</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Mathematics | Mechanical | Production and Processing | Design</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Control Precision | Near Vision | Problem Sensitivity | Deductive Reasoning | Selective Attention | Rate Control | Multilimb Coordination | Visualization | Information Ordering | Oral Comprehension | Category Flexibility | Inductive Reasoning | Oral Expression | Written Comprehension | Reaction Time | Perceptual Speed | Flexibility of Closure | Speech Clarity | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Pace Determined by Speed of Equipment | Time Pressure | Freedom to Make Decisions | Indoors, Environmentally Controlled | Spend Time Making Repetitive Motions | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Determine Tasks, Priorities and Goals | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Contact With Others | Health and Safety of Other Workers | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Computer Numerically Controlled Tool Operators | Computer Numerically Controlled Tool Programmers | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Millwrights | Model Makers, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Structural Metal Fabricators and Fitters | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up and operate a variety of machine tools to produce precision parts and instruments out of metal. Includes precision instrument makers who fabricate, modify, or repair mechanical instruments. May also fabricate and modify parts to make or repair machine tools or maintain industrial machines, applying knowledge of mechanics, mathematics, metal properties, layout, and machining procedures.</t>
+  </si>
+  <si>
+    <t>Advise clients about the materials being used for finished products. | Align and secure holding fixtures, cutting tools, attachments, accessories, or materials onto machines. | Calculate dimensions or tolerances, using instruments, such as micrometers or vernier calipers. | Check work pieces to ensure that they are properly lubricated or cooled. | Confer with engineering, supervisory, or manufacturing personnel to exchange technical information. | Confer with numerical control programmers to check and ensure that new programs or machinery will function properly and that output will meet specifications. | Design fixtures, tooling, or experimental parts to meet special engineering needs. | Diagnose machine tool malfunctions to determine need for adjustments or repairs. | Dismantle machines or equipment, using hand tools or power tools to examine parts for defects and replace defective parts where needed. | Dispose of scrap or waste material in accordance with company policies and environmental regulations. | Establish work procedures for fabricating new structural products, using a variety of metalworking machines. | Evaluate machining procedures and recommend changes or modifications for improved efficiency or adaptability. | Fit and assemble parts to make or repair machine tools. | Install experimental parts or assemblies, such as hydraulic systems, electrical wiring, lubricants, or batteries into machines or mechanisms. | Install repaired parts into equipment or install new equipment. | Lay out, measure, and mark metal stock to display placement of cuts. | Machine parts to specifications, using machine tools, such as lathes, milling machines, shapers, or grinders. | Maintain machine tools in proper operational condition. | Measure, examine, or test completed units to check for defects and ensure conformance to specifications, using precision instruments, such as micrometers. | Monitor the feed and speed of machines during the machining process. | Operate equipment to verify operational efficiency. | Prepare working sketches for the illustration of product appearance. | Program computers or electronic instruments, such as numerically controlled machine tools. | Separate scrap waste and related materials for reuse, recycling, or disposal. | Set up or operate metalworking, brazing, heat-treating, welding, or cutting equipment. | Set up, adjust, or operate basic or specialized machine tools used to perform precision machining operations. | Study sample parts, blueprints, drawings, or engineering information to determine methods or sequences of operations needed to fabricate products. | Support metalworking projects from planning and fabrication through assembly, inspection, and testing, using knowledge of machine functions, metal properties, and mathematics. | Test experimental models under simulated operating conditions, for purposes such as development, standardization, or feasibility of design.</t>
+  </si>
+  <si>
+    <t>51-4051.00</t>
+  </si>
+  <si>
+    <t>Metal-Refining Furnace Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Arc and Argon Oxygen Decarburization Melter (ARC and AOD Melter) | Automatic Furnace Operator | Central Melt Specialist | Control Room Operator | Electric Melt Operator | Furnace Operator | Melt Room Operator | Melter | Vacuum Melter | Vessel Operator</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Process control software | Process safety management software | Production tracking system software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Public Safety and Security | Administration and Management | Education and Training</t>
+  </si>
+  <si>
+    <t>Control Precision | Problem Sensitivity | Manual Dexterity | Near Vision | Reaction Time | Arm-Hand Steadiness | Selective Attention | Information Ordering | Multilimb Coordination | Hearing Sensitivity | Depth Perception | Extent Flexibility | Static Strength | Rate Control | Perceptual Speed | Deductive Reasoning | Response Orientation | Finger Dexterity | Flexibility of Closure | Inductive Reasoning | Oral Expression | Glare Sensitivity | Visual Color Discrimination | Trunk Strength | Auditory Attention</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Pace Determined by Speed of Equipment | Exposed to Hazardous Conditions | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Making Repetitive Motions | Indoors, Not Environmentally Controlled | Freedom to Make Decisions | Importance of Repeating Same Tasks | Consequence of Error | Exposed to Hazardous Equipment | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Biomass Plant Technicians | Chemical Equipment Operators and Tenders | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Cooling and Freezing Equipment Operators and Tenders | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Gas Compressor and Gas Pumping Station Operators | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Pourers and Casters, Metal | Pump Operators, Except Wellhead Pumpers | Refractory Materials Repairers, Except Brickmasons | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Stationary Engineers and Boiler Operators | Welders, Cutters, Solderers, and Brazers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Operate or tend furnaces, such as gas, oil, coal, electric-arc or electric induction, open-hearth, or oxygen furnaces, to melt and refine metal before casting or to produce specified types of steel.</t>
+  </si>
+  <si>
+    <t>Direct work crews in the cleaning and repair of furnace walls and flooring. | Drain, transfer, or remove molten metal from furnaces, and place it into molds, using hoists, pumps, or ladles. | Draw smelted metal samples from furnaces or kettles for analysis, and calculate types and amounts of materials needed to ensure that materials meet specifications. | Inspect furnaces and equipment to locate defects and wear. | Kindle fires, and shovel fuel and other materials into furnaces or onto conveyors by hand, with hoists, or by directing crane operators. | Observe air and temperature gauges or metal color and fluidity, and turn fuel valves or adjust controls to maintain required temperatures. | Observe operations inside furnaces, using television screens, to ensure that problems do not occur. | Operate controls to move or discharge metal workpieces from furnaces. | Prepare material to load into furnaces, including cleaning, crushing, or applying chemicals, by using crushing machines, shovels, rakes, or sprayers. | Record production data, and maintain production logs. | Regulate supplies of fuel and air, or control flow of electric current and water coolant to heat furnaces and adjust temperatures. | Remove impurities from the surface of molten metal, using strainers. | Scrape accumulations of metal oxides from floors, molds, and crucibles, and sift and store them for reclamation. | Sprinkle chemicals over molten metal to bring impurities to the surface. | Weigh materials to be charged into furnaces, using scales.</t>
+  </si>
+  <si>
+    <t>51-4052.00</t>
+  </si>
+  <si>
+    <t>Pourers and Casters, Metal</t>
+  </si>
+  <si>
+    <t>Caster | Casting Machine Operator | Casting Operator | DC Caster (Direct Chill Caster) | Die Cast Machine Operator | Die Casting Machine Operator | Iron Pourer | Melter | Metal Handler | Pourer</t>
+  </si>
+  <si>
+    <t>Husky Injection Molding Systems Shotscope NX | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>English Language</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Control Precision | Manual Dexterity | Near Vision | Reaction Time | Multilimb Coordination | Perceptual Speed | Trunk Strength | Finger Dexterity | Selective Attention | Category Flexibility | Problem Sensitivity | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Not Environmentally Controlled | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Foundry Mold and Coremakers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Metal-Refining Furnace Operators and Tenders | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Refractory Materials Repairers, Except Brickmasons | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate hand-controlled mechanisms to pour and regulate the flow of molten metal into molds to produce castings or ingots.</t>
+  </si>
+  <si>
+    <t>Add metal to molds to compensate for shrinkage. | Assemble and embed cores in casting frames, using hand tools and equipment. | Collect samples, or signal workers to sample metal for analysis. | Examine molds to ensure they are clean, smooth, and properly coated. | Load specified amounts of metal and flux into furnaces or clay crucibles. | Position equipment such as ladles, grinding wheels, pouring nozzles, or crucibles, or signal other workers to position equipment. | Pour and regulate the flow of molten metal into molds and forms to produce ingots or other castings, using ladles or hand-controlled mechanisms. | Pull levers to lift ladle stoppers and to allow molten steel to flow into ingot molds to specified heights. | Read temperature gauges and observe color changes, adjusting furnace flames, torches, or electrical heating units as necessary to melt metal to specifications. | Remove metal ingots or cores from molds, using hand tools, cranes, and chain hoists. | Remove solidified steel or slag from pouring nozzles, using long bars or oxygen burners. | Repair and maintain metal forms and equipment, using hand tools, sledges, and bars. | Skim slag or remove excess metal from ingots or equipment, using hand tools, strainers, rakes, or burners, collecting scrap for recycling. | Stencil identifying information on ingots and pigs, using special hand tools. | Transport metal ingots to storage areas, using forklifts. | Turn valves to circulate water through cores, or spray water on filled molds to cool and solidify metal.</t>
+  </si>
+  <si>
+    <t>51-4061.00</t>
+  </si>
+  <si>
+    <t>Model Makers, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>CNC Machinist (Computer Numerical Control Machinist) | CNC Programmer (Computer Numerical Control Programmer) | Metal Model Maker | Model Builder | Model Maker | Model Maker Machinist | Model Technician (Model Tech) | Molding Technician (Molding Tech) | Pattern Finisher | Prototype Special Build</t>
+  </si>
+  <si>
+    <t>CNC Software Mastercam | Microsoft Excel | Microsoft Office software | Microsoft Word | PTC Creo Parametric</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring</t>
+  </si>
+  <si>
+    <t>Mechanical | Mathematics | Production and Processing | Design | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Near Vision | Visualization | Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Control Precision | Information Ordering | Written Comprehension | Problem Sensitivity | Oral Comprehension | Reaction Time | Deductive Reasoning | Selective Attention | Multilimb Coordination | Rate Control | Perceptual Speed | Category Flexibility | Inductive Reasoning | Written Expression | Oral Expression | Auditory Attention | Far Vision | Trunk Strength | Static Strength</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Computer Numerically Controlled Tool Operators | Computer Numerically Controlled Tool Programmers | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Industrial Machinery Mechanics | Layout Workers, Metal and Plastic | Machinists | Mechanical Drafters | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Model Makers, Wood | Molders, Shapers, and Casters, Except Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Patternmakers, Metal and Plastic | Sheet Metal Workers | Structural Metal Fabricators and Fitters | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Set up and operate machines, such as lathes, milling and engraving machines, and jig borers to make working models of metal or plastic objects. Includes template makers.</t>
+  </si>
+  <si>
+    <t>Align, fit, and join parts, using bolts and screws or by welding or gluing. | Assemble mechanical, electrical, and electronic components into models or prototypes, using hand tools, power tools, and fabricating machines. | Consult and confer with engineering personnel to discuss developmental problems and to recommend product modifications. | Cut, shape, and form metal parts, using lathes, power saws, snips, power brakes and shears, files, and mallets. | Devise and construct tools, dies, molds, jigs, and fixtures, or modify existing tools and equipment. | Drill, countersink, and ream holes in parts and assemblies for bolts, screws, and other fasteners, using power tools. | Grind, file, and sand parts to finished dimensions. | Inspect and test products to verify conformance to specifications, using precision measuring instruments or circuit testers. | Lay out and mark reference points and dimensions on materials, using measuring instruments and drawing or scribing tools. | Program computer numerical control (CNC) machines to fabricate model parts. | Record specifications, production operations, and final dimensions of models for use in establishing operating standards and procedures. | Rework or alter component model or parts as required to ensure that products meet standards. | Set up and operate machines, such as lathes, drill presses, punch presses, or bandsaws, to fabricate prototypes or models. | Study blueprints, drawings, and sketches to determine material dimensions, required equipment, and operations sequences. | Use computer-aided design (CAD) and computer-aided manufacturing (CAM) software or hardware to fabricate model parts. | Wire and solder electrical and electronic connections and components.</t>
+  </si>
+  <si>
+    <t>51-4062.00</t>
+  </si>
+  <si>
+    <t>Patternmakers, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Die Cast Die Maker | Fixture Builder | Layout Technician | Metal Pattern Maker | Pattern Maker | Pattern Maker Programmer | Pattern Repair Person | Patternmaker | Wax Molder</t>
+  </si>
+  <si>
+    <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | Mastercam computer-aided design and manufacturing software | Microsoft Excel | Microsoft Outlook</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Mathematics | Design | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Problem Sensitivity | Visualization | Manual Dexterity | Control Precision | Finger Dexterity | Selective Attention | Information Ordering | Deductive Reasoning | Category Flexibility | Inductive Reasoning | Oral Expression | Written Comprehension | Oral Comprehension | Speech Recognition | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Exposed to Contaminants | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Exposed to Hazardous Equipment | Telephone Conversations | Spend Time Standing | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | E-Mail | Physical Proximity | Work Outcomes and Results of Other Workers | Health and Safety of Other Workers | Indoors, Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Etchers and Engravers | Fabric and Apparel Patternmakers | Grinding and Polishing Workers, Hand | Layout Workers, Metal and Plastic | Machinists | Mechanical Drafters | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Model Makers, Metal and Plastic | Model Makers, Wood | Molders, Shapers, and Casters, Except Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Patternmakers, Wood | Sewers, Hand | Sheet Metal Workers | Structural Metal Fabricators and Fitters | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers</t>
+  </si>
+  <si>
+    <t>Lay out, machine, fit, and assemble castings and parts to metal or plastic foundry patterns, core boxes, or match plates.</t>
+  </si>
+  <si>
+    <t>Apply plastic-impregnated fabrics or coats of sealing wax or lacquer to patterns used to produce plastic. | Assemble pattern sections, using hand tools, bolts, screws, rivets, glue, or welding equipment. | Clean and finish patterns or templates, using emery cloths, files, scrapers, and power grinders. | Construct platforms, fixtures, and jigs for holding and placing patterns. | Create computer models of patterns or parts, using modeling software. | Design and create templates, patterns, or coreboxes according to work orders, sample parts, or mockups. | Lay out and draw or scribe patterns onto material, using compasses, protractors, rulers, scribes, or other instruments. | Mark identification numbers or symbols onto patterns or templates. | Paint or lacquer patterns. | Program computerized numerical control machine tools. | Read and interpret blueprints or drawings of parts to be cast or patterns to be made, compute dimensions, and plan operational sequences. | Repair and rework templates and patterns. | Select pattern materials such as wood, resin, and fiberglass. | Set up and operate machine tools, such as milling machines, lathes, drill presses, and grinders, to machine castings or patterns. | Verify conformance of patterns or template dimensions to specifications, using measuring instruments such as calipers, scales, and micrometers.</t>
+  </si>
+  <si>
+    <t>51-4071.00</t>
+  </si>
+  <si>
+    <t>Foundry Mold and Coremakers</t>
+  </si>
+  <si>
+    <t>Core Machine Operator | Core Maker | Core Stripper | Coremaker | Green Sand Molder | Mold Maker | Mold Operator | Molder | No Bake Molder | Sand Molder</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | CNC Software Mastercam | Dassault Systemes SolidWorks | Inventory tracking software | Machine control software | PTC Creo Parametric</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>English Language | Mechanical | Education and Training | Production and Processing | Administration and Management | Physics | Design | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Manual Dexterity | Static Strength | Arm-Hand Steadiness | Finger Dexterity | Multilimb Coordination | Near Vision | Reaction Time | Problem Sensitivity | Auditory Attention | Control Precision | Selective Attention | Visualization | Information Ordering | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Not Environmentally Controlled | Exposed to Contaminants | Exposed to Very Hot or Cold Temperatures | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Hazardous Equipment | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Importance of Being Exact or Accurate | Spend Time Making Repetitive Motions | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Exposed to Hazardous Conditions | Exposed to Minor Burns, Cuts, Bites, or Stings | Work Outcomes and Results of Other Workers | Impact of Decisions on Co-workers or Company Results | Pace Determined by Speed of Equipment | Frequency of Decision Making | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Fiberglass Laminators and Fabricators | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Patternmakers, Metal and Plastic | Refractory Materials Repairers, Except Brickmasons | Shoe Machine Operators and Tenders | Structural Metal Fabricators and Fitters | Terrazzo Workers and Finishers | Tire Builders | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Make or form wax or sand cores or molds used in the production of metal castings in foundries.</t>
+  </si>
+  <si>
+    <t>Clean and smooth molds, cores, and core boxes, and repair surface imperfections. | Cut spouts, runner holes, and sprue holes into molds. | Form and assemble slab cores around patterns, and position wire in mold sections to reinforce molds, using hand tools and glue. | Lift upper mold sections from lower sections, and remove molded patterns. | Move and position workpieces, such as mold sections, patterns, and bottom boards, using cranes, or signal others to move workpieces. | Operate ovens or furnaces to bake cores or to melt, skim, and flux metal. | Position cores into lower sections of molds, and reassemble molds for pouring. | Position patterns inside mold sections, and clamp sections together. | Pour molten metal into molds, manually or with crane ladles. | Rotate sweep boards around spindles to make symmetrical molds for convex impressions. | Sift and pack sand into mold sections, core boxes, and pattern contours, using hand or pneumatic ramming tools. | Sprinkle or spray parting agents onto patterns and mold sections to facilitate removal of patterns from molds. | Tend machines that bond cope and drag together to form completed shell molds.</t>
+  </si>
+  <si>
+    <t>51-4072.00</t>
+  </si>
+  <si>
+    <t>Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Core Machine Operator | Die Cast Technician | Diecast Machine Operator | Machine Operator | Mold Setter | Mold Technician | Molder | Process Technician | Production Technician</t>
+  </si>
+  <si>
+    <t>FANUC Robotics iRVision | HotFlo! Die-Shot Monitor | Intera Systems Hawk-i | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | RobotWare DieCast | SAP software | Visi-Trak True-Trak 20/20</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Reading Comprehension | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Mathematics</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Multilimb Coordination | Control Precision | Deductive Reasoning | Information Ordering | Perceptual Speed | Near Vision | Speech Clarity | Trunk Strength | Static Strength | Reaction Time | Rate Control | Finger Dexterity | Category Flexibility | Problem Sensitivity | Oral Expression | Written Comprehension | Oral Comprehension | Flexibility of Closure | Inductive Reasoning | Speech Recognition | Auditory Attention | Selective Attention | Visualization</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Time Pressure | Freedom to Make Decisions | Contact With Others | Pace Determined by Speed of Equipment | Exposed to Minor Burns, Cuts, Bites, or Stings | Determine Tasks, Priorities and Goals | Exposed to Very Hot or Cold Temperatures | Health and Safety of Other Workers | Physical Proximity | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend metal or plastic molding, casting, or coremaking machines to mold or cast metal or thermoplastic parts or products.</t>
+  </si>
+  <si>
+    <t>Adjust equipment and workpiece holding fixtures, such as mold frames, tubs, and cutting tables, to ensure proper functioning. | Connect water hoses to cooling systems of dies, using hand tools. | Cool products after processing to prevent distortion. | Install dies onto machines or presses and coat dies with parting agents, according to work order specifications. | Inventory and record quantities of materials and finished products, requisitioning additional supplies as necessary. | Maintain inventories of materials. | Measure and visually inspect products for surface and dimension defects to ensure conformance to specifications, using precision measuring instruments. | Mix and measure compounds, or weigh premixed compounds, and dump them into machine tubs, cavities, or molds. | Observe continuous operation of automatic machines to ensure that products meet specifications and to detect jams or malfunctions, making adjustments as necessary. | Observe meters and gauges to verify and record temperatures, pressures, and press-cycle times. | Obtain and move specified patterns to work stations, manually or using hoists, and secure patterns to machines, using wrenches. | Operate hoists to position dies or patterns on foundry floors. | Perform maintenance work such as cleaning and oiling machines. | Position and secure workpieces on machines, and start feeding mechanisms. | Pour or load metal or sand into melting pots, furnaces, molds, or hoppers, using shovels, ladles, or machines. | Preheat tools, dies, plastic materials, or patterns, using blowtorches or other equipment. | Read specifications, blueprints, and work orders to determine setups, temperatures, and time settings required to mold, form, or cast plastic materials, as well as to plan production sequences. | Remove finished or cured products from dies or molds, using hand tools, air hoses, and other equipment, stamping identifying information on products when necessary. | Remove parts, such as dies, from machines after production runs are finished. | Repair or replace damaged molds, pipes, belts, chains, or other equipment, using hand tools, hand-powered presses, or jib cranes. | Select and install blades, tools, or other attachments for each operation. | Select coolants and lubricants, and start their flow. | Set up, operate, or tend metal or plastic molding, casting, or coremaking machines to mold or cast metal or thermoplastic parts or products. | Skim or pour dross, slag, or impurities from molten metal, using ladles, rakes, hoes, spatulas, or spoons. | Smooth and clean inner surfaces of molds, using brushes, scrapers, air hoses, or grinding wheels, and fill imperfections with refractory material. | Spray, smoke, or coat molds with compounds to lubricate or insulate molds, using acetylene torches or sprayers. | Trim excess material from parts, using knives, and grind scrap plastic into powder for reuse. | Turn valves and dials of machines to regulate pressure, temperature, and speed and feed rates, and to set cycle times. | Unload finished products from conveyor belts, pack them in containers, and place containers in warehouses.</t>
+  </si>
+  <si>
+    <t>51-4081.00</t>
+  </si>
+  <si>
+    <t>Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>CNC Machine Setter (Computer Numerically Controlled Machine Setter) | Cell Technician | Fabrication Set-Up Person | Injection Molding Technician | Machine Operator | Machine Technician | Mold Setter | Production Operator | Shear Operator | Tooling Set-Up Person</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Email software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Reading Comprehension | Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Mathematics | English Language | Design</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Control Precision | Near Vision | Manual Dexterity | Problem Sensitivity | Visualization | Information Ordering | Speech Recognition | Far Vision | Reaction Time | Multilimb Coordination | Finger Dexterity | Selective Attention | Written Comprehension | Oral Comprehension | Speech Clarity | Auditory Attention | Hearing Sensitivity | Extent Flexibility | Rate Control | Perceptual Speed | Flexibility of Closure | Category Flexibility | Inductive Reasoning | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Time Pressure | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Pace Determined by Speed of Equipment | Freedom to Make Decisions | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Computer Numerically Controlled Tool Operators | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend more than one type of cutting or forming machine tool or robot.</t>
+  </si>
+  <si>
+    <t>Align layout marks with dies or blades. | Change worn machine accessories, such as cutting tools or brushes, using hand tools. | Compute data, such as gear dimensions or machine settings, applying knowledge of shop mathematics. | Extract or lift jammed pieces from machines, using fingers, wire hooks, or lift bars. | Inspect workpieces for defects, and measure workpieces to determine accuracy of machine operation, using rules, templates, or other measuring instruments. | Instruct other workers in machine set-up and operation. | Make minor electrical and mechanical repairs and adjustments to machines and notify supervisors when major service is required. | Measure and mark reference points and cutting lines on workpieces, using traced templates, compasses, and rules. | Move controls or mount gears, cams, or templates in machines to set feed rates and cutting speeds, depths, and angles. | Observe machine operation to detect workpiece defects or machine malfunctions, adjusting machines as necessary. | Perform minor machine maintenance, such as oiling or cleaning machines, dies, or workpieces, or adding coolant to machine reservoirs. | Position, adjust, and secure stock material or workpieces against stops, on arbors, or in chucks, fixtures, or automatic feeding mechanisms, manually or using hoists. | Read blueprints or job orders to determine product specifications and tooling instructions and to plan operational sequences. | Record operational data, such as pressure readings, lengths of strokes, feed rates, or speeds. | Remove burrs, sharp edges, rust, or scale from workpieces, using files, hand grinders, wire brushes, or power tools. | Select the proper coolants and lubricants and start their flow. | Select, install, and adjust alignment of drills, cutters, dies, guides, and holding devices, using templates, measuring instruments, and hand tools. | Set machine stops or guides to specified lengths as indicated by scales, rules, or templates. | Set up and operate machines, such as lathes, cutters, shears, borers, millers, grinders, presses, drills, or auxiliary machines, to make metallic and plastic workpieces. | Start machines and turn handwheels or valves to engage feeding, cooling, and lubricating mechanisms. | Write programs for computer numerical control (CNC) machines to cut metal and plastic materials.</t>
+  </si>
+  <si>
+    <t>51-4111.00</t>
+  </si>
+  <si>
+    <t>Tool and Die Makers</t>
+  </si>
+  <si>
+    <t>Die Machinist | Die Repair Laborer | Die Repair Technician (Die Repair Tech) | Jig and Fixture Repairer | Tool Maker | Tool Repairer | Tool and Die Machinist | Tool and Die Maker | Tool and Fixture Specialist | Trim Die Maker</t>
+  </si>
+  <si>
+    <t>1CadCam Unigraphics | Autodesk AutoCAD | Autodesk Inventor | Bentley MicroStation | CNC Mastercam | Cimatron CimatronE Master | DP Technology ESPRIT | Dassault Systemes CATIA | Dassault Systemes SolidWorks | JobPack MES Scheduler | Kubotek USA KeyCreator | Logopress | MAKER CAD/CAM Services DIEMAKER | Mastercam computer-aided design and manufacturing software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | NC verification software | OPEN MIND Technologies hyperMILL | PTC Creo Parametric | SAP software | Seco Tools Seco Point | Striker Systems SS-Die Design | Striker Systems SS-Draw Form | Striker Systems SS-Strip Design | VX Corporation VX Mold &amp; Die | Vero International VISI-Mould | Virtual Gibbs CADD/CAM | data M Software COPRA MetalBender</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Learning | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Mathematics | Production and Processing | Design | English Language</t>
+  </si>
+  <si>
+    <t>Visualization | Near Vision | Problem Sensitivity | Control Precision | Finger Dexterity | Manual Dexterity | Information Ordering | Category Flexibility | Selective Attention | Arm-Hand Steadiness | Multilimb Coordination | Deductive Reasoning | Oral Expression | Oral Comprehension | Speech Clarity | Speech Recognition | Mathematical Reasoning | Inductive Reasoning | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Exposed to Hazardous Equipment | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Contact With Others | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Consequence of Error | Impact of Decisions on Co-workers or Company Results | Exposed to Contaminants</t>
+  </si>
+  <si>
+    <t>Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Layout Workers, Metal and Plastic | Machinists | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Model Makers, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Patternmakers, Metal and Plastic | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Structural Metal Fabricators and Fitters | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Analyze specifications, lay out metal stock, set up and operate machine tools, and fit and assemble parts to make and repair dies, cutting tools, jigs, fixtures, gauges, and machinists' hand tools.</t>
+  </si>
+  <si>
+    <t>Conduct test runs with completed tools or dies to ensure that parts meet specifications, making adjustments as necessary. | Cut, shape, and trim blanks or blocks to specified lengths or shapes, using power saws, power shears, rules, and hand tools. | Design jigs, fixtures, and templates for use as work aids in the fabrication of parts or products. | Develop and design new tools and dies, using computer-aided design software. | File, grind, shim, and adjust different parts to properly fit them together. | Fit and assemble parts to make, repair, or modify dies, jigs, gauges, and tools, using machine tools, hand tools, or welders. | Inspect finished dies for smoothness, contour conformity, and defects. | Lift, position, and secure machined parts on surface plates or worktables, using hoists, vises, v-blocks, or angle plates. | Measure, mark, and scribe metal or plastic stock to lay out machining, using instruments such as protractors, micrometers, scribes, or rulers. | Select metals to be used from a range of metals and alloys, based on properties such as hardness or heat tolerance. | Set pyrometer controls of heat-treating furnaces and feed or place parts, tools, or assemblies into furnaces to harden. | Set up and operate conventional or computer numerically controlled machine tools such as lathes, milling machines, or grinders to cut, bore, grind, or otherwise shape parts to prescribed dimensions and finishes. | Set up and operate drill presses to drill and tap holes in parts for assembly. | Smooth and polish flat and contoured surfaces of parts or tools, using scrapers, abrasive stones, files, emery cloths, or power grinders. | Study blueprints, sketches, models, or specifications to plan sequences of operations for fabricating tools, dies, or assemblies. | Verify dimensions, alignments, and clearances of finished parts for conformance to specifications, using measuring instruments such as calipers, gauge blocks, micrometers, or dial indicators. | Visualize and compute dimensions, sizes, shapes, and tolerances of assemblies, based on specifications.</t>
+  </si>
+  <si>
+    <t>51-4121.00</t>
+  </si>
+  <si>
+    <t>Welders, Cutters, Solderers, and Brazers</t>
+  </si>
+  <si>
+    <t>Assembly Line Brazer | Brazer | Fabrication Welder | MIG Welder (Metal Inert Gas Welder) | Maintenance Welder | Solderer | TIG Welder (Tungsten Inert Gas Welder) | Welder | Welder Fitter | Wirer</t>
+  </si>
+  <si>
+    <t>EZ Pipe | Fred's Tip Cartridge Picker | IBM Notes | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | OmniFleet Equipment Maintenance Management | Oracle Database | Recordkeeping software | Scientific Software Group Filter Drain FD | Value Analysis</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Problem Sensitivity | Finger Dexterity | Control Precision | Manual Dexterity | Deductive Reasoning | Oral Comprehension | Selective Attention</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Contact With Others | Indoors, Not Environmentally Controlled | Spend Time Standing</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Cutting and Slicing Machine Setters, Operators, and Tenders | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Equipment Assemblers | Engine and Other Machine Assemblers | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machinists | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Structural Metal Fabricators and Fitters | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Use hand-welding, flame-cutting, hand-soldering, or brazing equipment to weld or join metal components or to fill holes, indentations, or seams of fabricated metal products.</t>
+  </si>
+  <si>
+    <t>Align and clamp workpieces together, using rules, squares, or hand tools, or position items in fixtures, jigs, or vises. | Analyze engineering drawings, blueprints, specifications, sketches, work orders, and material safety data sheets to plan layout, assembly, and operations. | Check grooves, angles, or gap allowances, using micrometers, calipers, and precision measuring instruments. | Chip or grind off excess weld, slag, or spatter, using hand scrapers or power chippers, portable grinders, or arc-cutting equipment. | Clean or degrease parts, using wire brushes, portable grinders, or chemical baths. | Connect and turn regulator valves to activate and adjust gas flow and pressure so that desired flames are obtained. | Detect faulty operation of equipment or defective materials and notify supervisors. | Determine required equipment and welding methods, applying knowledge of metallurgy, geometry, and welding techniques. | Develop templates and models for welding projects, using mathematical calculations based on blueprint information. | Examine workpieces for defects and measure workpieces with straightedges or templates to ensure conformance with specifications. | Grind, cut, buff, or bend edges of workpieces to be joined to ensure snug fit, using power grinders and hand tools. | Guide and direct flames or electrodes on or across workpieces to straighten, bend, melt, or build up metal. | Hammer out bulges or bends in metal workpieces. | Ignite torches or start power supplies and strike arcs by touching electrodes to metals being welded, completing electrical circuits. | Mark or tag material with proper job number, piece marks, and other identifying marks as required. | Melt and apply solder along adjoining edges of workpieces to solder joints, using soldering irons, gas torches, or electric-ultrasonic equipment. | Melt and apply solder to fill holes, indentations, or seams of fabricated metal products, using soldering equipment. | Monitor the fitting, burning, and welding processes to avoid overheating of parts or warping, shrinking, distortion, or expansion of material. | Operate metal shaping, straightening, and bending machines, such as brakes and shears. | Operate safety equipment and use safe work habits. | Position and secure workpieces, using hoists, cranes, wire, and banding machines or hand tools. | Preheat workpieces prior to welding or bending, using torches or heating furnaces. | Prepare all material surfaces to be welded, ensuring that there is no loose or thick scale, slag, rust, moisture, grease, or other foreign matter. | Recognize, set up, and operate hand and power tools common to the welding trade, such as shielded metal arc and gas metal arc welding equipment. | Repair products by dismantling, straightening, reshaping, and reassembling parts, using cutting torches, straightening presses, and hand tools. | Select and install torches, torch tips, filler rods, and flux, according to welding chart specifications or types and thicknesses of metals. | Set up and use ladders and scaffolding as necessary to complete work. | Use fire suppression methods in industrial emergencies. | Weld components in flat, vertical, or overhead positions. | Weld separately or in combination, using aluminum, stainless steel, cast iron, and other alloys.</t>
+  </si>
+  <si>
+    <t>51-4122.00</t>
+  </si>
+  <si>
+    <t>Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Braze Operator | Certified Welder | Fabricator | Finishing Technician (Finishing Tech) | Laser Operator | Machine Operator | Mig Welder | Spot Welder | Weld Technician (Weld Tech) | Welding Operator</t>
+  </si>
+  <si>
+    <t>Email software | Linux | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | SAP software | Tool center point TCP setting software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Reading Comprehension | Monitoring</t>
+  </si>
+  <si>
+    <t>Production and Processing | Administration and Management | Design</t>
+  </si>
+  <si>
+    <t>Near Vision | Control Precision | Visualization | Arm-Hand Steadiness | Manual Dexterity | Multilimb Coordination | Selective Attention | Information Ordering | Problem Sensitivity | Perceptual Speed | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Oral Expression | Speech Recognition | Far Vision | Extent Flexibility | Trunk Strength | Reaction Time | Rate Control | Finger Dexterity | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Time Pressure | Spend Time Standing | Exposed to Contaminants | Spend Time Making Repetitive Motions | Health and Safety of Other Workers | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Exposed to Minor Burns, Cuts, Bites, or Stings | Coordinate or Lead Others in Accomplishing Work Activities | Indoors, Not Environmentally Controlled | Exposed to Very Hot or Cold Temperatures | Consequence of Error | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Contact With Others | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Equipment Assemblers | Engine and Other Machine Assemblers | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machinists | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Structural Metal Fabricators and Fitters | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welders, Cutters, Solderers, and Brazers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend welding, soldering, or brazing machines or robots that weld, braze, solder, or heat treat metal products, components, or assemblies. Includes workers who operate laser cutters or laser-beam machines.</t>
+  </si>
+  <si>
+    <t>Add chemicals or materials to workpieces or machines to facilitate bonding or to cool workpieces. | Anneal finished workpieces to relieve internal stress. | Assemble, align, and clamp workpieces into holding fixtures to bond, heat-treat, or solder fabricated metal components. | Clean, lubricate, maintain, and adjust equipment to maintain efficient operation, using air hoses, cleaning fluids, and hand tools. | Compute and record settings for new work, applying knowledge of metal properties, principles of welding, and shop mathematics. | Conduct trial runs before welding, soldering, or brazing, and make necessary adjustments to equipment. | Correct problems by adjusting controls or by stopping machines and opening holding devices. | Devise or build fixtures or jigs used to hold parts in place during welding, brazing, or soldering. | Dress electrodes, using tip dressers, files, emery cloths, or dressing wheels. | Fill hoppers and position spouts to direct flow of flux or manually brush flux onto seams of workpieces. | Give directions to other workers regarding machine set-up and use. | Immerse completed workpieces into water or acid baths to cool and clean components. | Inspect, measure, or test completed metal workpieces to ensure conformance to specifications, using measuring and testing devices. | Lay out, fit, or connect parts to be bonded, calculating production measurements, as necessary. | Load or feed workpieces into welding machines to join or bond components. | Mark weld points and positions of components on workpieces, using rules, squares, templates, or scribes. | Observe meters, gauges, or machine operations to ensure that soldering or brazing processes meet specifications. | Prepare metal surfaces or workpieces, using hand-operated equipment, such as grinders, cutters, or drills. | Read blueprints, work orders, or production schedules to determine product or job instructions or specifications. | Record operational information on specified production reports. | Remove completed workpieces or parts from machinery, using hand tools. | Select torch tips, alloys, flux, coil, tubing, or wire, according to metal types or thicknesses, data charts, or records. | Select, position, align, and bolt jigs, holding fixtures, guides, or stops onto machines, using measuring instruments and hand tools. | Set dials and timing controls to regulate electrical current, gas flow pressure, heating or cooling cycles, or shut-off. | Set up, operate, or tend welding machines that join or bond components to fabricate metal products or assemblies. | Start, monitor, and adjust robotic welding production lines. | Tend auxiliary equipment used in welding processes. | Transfer components, metal products, or assemblies, using moving equipment. | Turn and press knobs and buttons or enter operating instructions into computers to adjust and start welding machines.</t>
+  </si>
+  <si>
+    <t>51-4191.00</t>
+  </si>
+  <si>
+    <t>Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Batch Heat Treat Operator | Burner | Coating Line Worker | Furnace Operator | Heat Treat Furnace Operator | Heat Treat Operator | Heat Treat Technician | Heat Treater | Scarf and Anneal Operator</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mathematics</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Multilimb Coordination | Reaction Time | Near Vision | Manual Dexterity | Problem Sensitivity | Trunk Strength | Static Strength | Control Precision | Information Ordering | Perceptual Speed | Selective Attention | Finger Dexterity | Stamina | Speech Clarity | Speech Recognition | Rate Control | Visualization | Flexibility of Closure | Deductive Reasoning | Oral Expression | Far Vision | Extent Flexibility | Response Orientation | Category Flexibility | Written Comprehension | Oral Comprehension | Auditory Attention | Depth Perception</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Not Environmentally Controlled | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Contact With Others | Pace Determined by Speed of Equipment | Exposed to Very Hot or Cold Temperatures | Spend Time Making Repetitive Motions | Spend Time Walking or Running | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Exposed to Hazardous Equipment</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Chemical Equipment Operators and Tenders | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Cooling and Freezing Equipment Operators and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Metal-Refining Furnace Operators and Tenders | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Refractory Materials Repairers, Except Brickmasons | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders | Welders, Cutters, Solderers, and Brazers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend heating equipment, such as heat-treating furnaces, flame-hardening machines, induction machines, soaking pits, or vacuum equipment to temper, harden, anneal, or heat treat metal or plastic objects.</t>
+  </si>
+  <si>
+    <t>Adjust controls to maintain temperatures and heating times, using thermal instruments and charts, dials and gauges of furnaces, and color of stock in furnaces to make setting determinations. | Clean oxides and scales from parts or fittings, using steam sprays or chemical and water baths. | Determine flame temperatures, current frequencies, heating cycles, and induction heating coils needed, based on degree of hardness required and properties of stock to be treated. | Determine types and temperatures of baths and quenching media needed to attain specified part hardness, toughness, and ductility, using heat-treating charts and knowledge of methods, equipment, and metals. | Examine parts to ensure metal shades and colors conform to specifications, using knowledge of metal heat-treating. | Heat billets, bars, plates, rods, and other stock to specified temperatures preparatory to forging, rolling, or processing, using oil, gas, or electrical furnaces. | Instruct new workers in machine operation. | Load parts into containers and place containers on conveyors to be inserted into furnaces, or insert parts into furnaces. | Mount fixtures and industrial coils on machines, using hand tools. | Mount workpieces in fixtures, on arbors, or between centers of machines. | Move controls to light gas burners and to adjust gas and water flow and flame temperature. | Position stock in furnaces, using tongs, chain hoists, or pry bars. | Read production schedules and work orders to determine processing sequences, furnace temperatures, and heat cycle requirements for objects to be heat-treated. | Record times that parts are removed from furnaces to document that objects have attained specified temperatures for specified times. | Reduce heat when processing is complete to allow parts to cool in furnaces or machinery. | Remove parts from furnaces after specified times, and air dry or cool parts in water, oil brine, or other baths. | Repair, replace, and maintain furnace equipment as needed, using hand tools. | Set and adjust speeds of reels and conveyors for prescribed time cycles to pass parts through continuous furnaces. | Set up and operate or tend machines, such as furnaces, baths, flame-hardening machines, and electronic induction machines, that harden, anneal, and heat-treat metal. | Signal forklift operators to deposit or extract containers of parts into and from furnaces and quenching rinse tanks. | Stamp heat-treatment identification marks on parts, using hammers and punches. | Start conveyors and open furnace doors to load stock, or signal crane operators to uncover soaking pits and lower ingots into them. | Test parts for hardness, using hardness testing equipment, or by examining and feeling samples.</t>
+  </si>
+  <si>
+    <t>51-4192.00</t>
+  </si>
+  <si>
+    <t>Layout Workers, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Development Mechanic | Layout Fabricator | Layout Fitter | Layout Inspector | Layout Man | Layout Mechanic | Layout Technician (Layout Tech) | Layout Worker</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Hexagon Metrology PC-DMIS | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | Optical Gaging Products Measure-X</t>
+  </si>
+  <si>
+    <t>Mathematics | Monitoring | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mathematics | Design | Mechanical | Production and Processing | English Language | Engineering and Technology | Building and Construction | Administration and Management | Computers and Electronics | Education and Training</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Visualization | Problem Sensitivity | Manual Dexterity | Information Ordering | Deductive Reasoning | Finger Dexterity | Selective Attention | Perceptual Speed | Flexibility of Closure | Mathematical Reasoning | Written Comprehension | Oral Comprehension | Trunk Strength | Multilimb Coordination | Control Precision | Number Facility | Category Flexibility | Inductive Reasoning | Oral Expression | Auditory Attention | Far Vision</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Exposed to Contaminants | Time Pressure | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Not Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Exposed to Very Hot or Cold Temperatures | Exposed to Hazardous Equipment | Spend Time Walking or Running | Exposed to Minor Burns, Cuts, Bites, or Stings | Contact With Others | Exposed to Extremely Bright or Inadequate Lighting Conditions | Spend Time Making Repetitive Motions | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Cabinetmakers and Bench Carpenters | Carpenters | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Machinists | Mechanical Drafters | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Model Makers, Metal and Plastic | Model Makers, Wood | Molders, Shapers, and Casters, Except Metal and Plastic | Patternmakers, Metal and Plastic | Patternmakers, Wood | Sheet Metal Workers | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Lay out reference points and dimensions on metal or plastic stock or workpieces, such as sheets, plates, tubes, structural shapes, castings, or machine parts, for further processing. Includes shipfitters.</t>
+  </si>
+  <si>
+    <t>Add dimensional details to blueprints or drawings made by other workers. | Apply pigment to layout surfaces, using paint brushes. | Brace parts in position within hulls or ships for riveting or welding. | Compute layout dimensions, and determine and mark reference points on metal stock or workpieces for further processing, such as welding and assembly. | Design and prepare templates of wood, paper, or metal. | Fit and align fabricated parts to be welded or assembled. | Inspect machined parts to verify conformance to specifications. | Install doors, hatches, brackets, and clips. | Lay out and fabricate metal structural parts such as plates, bulkheads, and frames. | Lift and position workpieces in relation to surface plates, manually or with hoists, and using parallel blocks and angle plates. | Locate center lines and verify template positions, using measuring instruments such as gauge blocks, height gauges, and dial indicators. | Mark curves, lines, holes, dimensions, and welding symbols onto workpieces, using scribes, soapstones, punches, and hand drills. | Plan and develop layouts from blueprints and templates, applying knowledge of trigonometry, design, effects of heat, and properties of metals. | Plan locations and sequences of cutting, drilling, bending, rolling, punching, and welding operations, using compasses, protractors, dividers, and rules.</t>
+  </si>
+  <si>
+    <t>51-4193.00</t>
+  </si>
+  <si>
+    <t>Plating Machine Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Anodizer | Anodizing Line Operator | Chrome Plater | Coater Associate | Coater Operator | Electro Plater | Galvanizer | Line Operator | Machine Operator | Plater</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Hazardous materials management HMS software | Microsoft Excel | Microsoft Outlook | Microsoft Word | Oracle Advanced Procurement</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Monitoring | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mathematics | Chemistry | English Language | Mechanical | Engineering and Technology | Education and Training | Law and Government | Customer and Personal Service | Design | Public Safety and Security | Transportation</t>
+  </si>
+  <si>
+    <t>Near Vision | Control Precision | Oral Comprehension | Problem Sensitivity | Arm-Hand Steadiness | Manual Dexterity | Speech Clarity | Multilimb Coordination | Oral Expression | Selective Attention | Perceptual Speed | Flexibility of Closure | Category Flexibility | Information Ordering | Inductive Reasoning | Deductive Reasoning | Speech Recognition | Trunk Strength | Static Strength | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Time Pressure | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Importance of Being Exact or Accurate | Exposed to Hazardous Conditions | Work With or Contribute to a Work Group or Team | Indoors, Not Environmentally Controlled | Work Outcomes and Results of Other Workers | Contact With Others | Freedom to Make Decisions | Exposed to Very Hot or Cold Temperatures | Health and Safety of Other Workers | Spend Time Walking or Running | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Chemical Equipment Operators and Tenders | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Painting, Coating, and Decorating Workers | Pourers and Casters, Metal | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders | Tool Grinders, Filers, and Sharpeners | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend plating machines to coat metal or plastic products with chromium, zinc, copper, cadmium, nickel, or other metal to protect or decorate surfaces. Typically, the product being coated is immersed in molten metal or an electrolytic solution.</t>
+  </si>
+  <si>
+    <t>Adjust controls to set temperatures of coating substances and speeds of machines and equipment. | Adjust dials to regulate flow of current and voltage supplied to terminals to control plating processes. | Clean and maintain equipment, using water hoses and scrapers. | Clean workpieces, using wire brushes. | Determine sizes and compositions of objects to be plated, and amounts of electrical current and time required. | Examine completed objects to determine thicknesses of metal deposits, or measure thicknesses by using instruments such as micrometers. | Immerse objects to be coated or plated into cleaning solutions, or spray objects with conductive solutions to prepare them for plating. | Immerse workpieces in coating solutions or liquid metal or plastic for specified times. | Inspect coated or plated areas for defects, such as air bubbles or uneven coverage. | Maintain production records. | Measure and set stops, rolls, brushes, and guides on automatic feeders and conveying equipment or coating machines, using micrometers, rules, and hand tools. | Measure or weigh materials, using rulers, calculators, and scales. | Measure, mark, and mask areas to be excluded from plating. | Mix and test solutions, and turn valves to fill tanks with solutions. | Monitor and measure thicknesses of electroplating on component parts to verify conformance to specifications, using micrometers. | Observe gauges to ensure that machines are operating properly, making adjustments or stopping machines when problems occur. | Operate hoists to place workpieces onto machine feed carriages or spindles. | Operate sandblasting equipment to roughen and clean surfaces of workpieces. | Perform equipment maintenance, such as cleaning tanks and lubricating moving parts of conveyors. | Place plated or coated materials on racks and transfer them to ovens to dry for specified periods of time. | Position and feed materials into processing machines, by hand or by using automated equipment. | Position containers to receive parts, and load or unload materials in containers, using dollies or handtrucks. | Position objects to be plated in frames, or suspend them from positive or negative terminals of power supplies. | Preheat workpieces in ovens. | Read production schedules to determine setups of equipment and machines. | Remove excess materials or impurities from objects, using air hoses or grinding machines. | Remove objects from solutions at periodic intervals and observe objects to verify conformance to specifications. | Replace worn parts and adjust equipment components, using hand tools. | Rinse coated objects in cleansing liquids and dry them with cloths, centrifugal driers, or by tumbling in sawdust-filled barrels. | Set up, operate, or tend plating or coating machines to coat metal or plastic products with chromium, zinc, copper, cadmium, nickel, or other metal to protect or decorate surfaces. | Suspend objects, such as parts or molds from cathode rods, or negative terminals, and immerse objects in plating solutions. | Suspend sticks or pieces of plating metal from anodes, or positive terminals, and immerse metal in plating solutions. | Test machinery to ensure that it is operating properly.</t>
+  </si>
+  <si>
+    <t>51-4194.00</t>
+  </si>
+  <si>
+    <t>Tool Grinders, Filers, and Sharpeners</t>
+  </si>
+  <si>
+    <t>Cutter Grinder | Finisher | Grinder | Grinder Operator | OD Grinder Operator (Outer Diameter Grinder Operator) | Saw Filer | Tool Grinder | Tool and Cutter Grinder</t>
+  </si>
+  <si>
+    <t>ANCA ToolRoom | Dassault Systemes SolidWorks | IBM Lotus Notes | Microsoft Excel | Vero Software Edgecam | Zoller</t>
+  </si>
+  <si>
+    <t>Mechanical | Mathematics | English Language</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Control Precision | Near Vision | Visualization | Problem Sensitivity | Selective Attention | Flexibility of Closure | Perceptual Speed | Reaction Time | Rate Control | Written Comprehension | Category Flexibility | Information Ordering | Deductive Reasoning | Auditory Attention | Hearing Sensitivity | Static Strength | Multilimb Coordination</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Pace Determined by Speed of Equipment | Spend Time Making Repetitive Motions | Exposed to Contaminants | Time Pressure | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Exposed to Minor Burns, Cuts, Bites, or Stings | Frequency of Decision Making | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Indoors, Not Environmentally Controlled | Exposed to Hazardous Equipment | Contact With Others | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sawing Machine Setters, Operators, and Tenders, Wood | Textile Cutting Machine Setters, Operators, and Tenders | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Perform precision smoothing, sharpening, polishing, or grinding of metal objects.</t>
+  </si>
+  <si>
+    <t>Attach workpieces to grinding machines and form specified sections and repair cracks, using welding or brazing equipment. | Compute numbers, widths, and angles of cutting tools, micrometers, scales, and gauges, and adjust tools to produce specified cuts. | Dress grinding wheels, according to specifications. | Duplicate workpiece contours, using tracer attachments. | File or finish surfaces of workpieces, using prescribed hand tools. | Fit parts together in pre-assembly to ensure that dimensions are accurate. | Inspect dies to detect defects, assess wear, and verify specifications, using micrometers, steel gauge pins, and loupes. | Inspect, feel, and measure workpieces to ensure that surfaces and dimensions meet specifications. | Monitor machine operations to determine whether adjustments are necessary, stopping machines when problems occur. | Perform basic maintenance, such as cleaning and lubricating machine parts. | Place workpieces in electroplating solutions or apply pigments to surfaces of workpieces to highlight ridges and grooves. | Remove and replace worn or broken machine parts, using hand tools. | Remove finished workpieces from machines and place them in boxes or on racks, setting aside pieces that are defective. | Select and mount grinding wheels on machines, according to specifications, using hand tools and applying knowledge of abrasives and grinding procedures. | Set up and operate grinding or polishing machines to grind metal workpieces, such as dies, parts, and tools. | Straighten workpieces and remove dents, using straightening presses and hammers. | Study blueprints or layouts of metal workpieces to determine grinding procedures, and to plan machine setups and operational sequences. | Turn valves to direct flow of coolant against cutting wheels and workpieces during grinding.</t>
+  </si>
+  <si>
+    <t>51-4199.00</t>
+  </si>
+  <si>
+    <t>Metal Workers and Plastic Workers, All Other</t>
+  </si>
+  <si>
+    <t>Fabrication Worker | Machine Operator | Metal Fabricator | Metal Worker | Plastic Fabricator | Plastics Worker | Production Machine Operator | Metal Finishing Worker | Shop Worker | Metal Processing Worker</t>
+  </si>
+  <si>
+    <t>Supervisory control and data acquisition SCADA software | Programmable logic controller PLC software | Statistical process control SPC software | Materials requirement planning MRP software | Computerized maintenance management system CMMS | Microsoft Excel | Microsoft Word | Email software | Inventory management systems | Enterprise resource planning ERP system | Database software | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Reading Comprehension | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Mathematics | English Language | Engineering and Technology | Chemistry | Design</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention</t>
+  </si>
+  <si>
+    <t>Indoors, Not Environmentally Controlled | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Exposed to Hazardous Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Physical Proximity | Pace Determined by Speed of Equipment | Health and Safety of Other Workers | Consequence of Error | Degree of Automation | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Machinists | Welders, Cutters, Solderers, and Brazers | Tool and Die Makers | Layout Workers, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Foundry Mold and Coremakers | Pourers and Casters, Metal | Metal-Refining Furnace Operators and Tenders | Model Makers, Metal and Plastic | Computer Numerically Controlled Tool Operators | Inspectors, Testers, Sorters, Samplers, and Weighers | Structural Metal Fabricators and Fitters | First-Line Supervisors of Production and Operating Workers | Production Workers, All Other</t>
+  </si>
+  <si>
+    <t>All metal workers and plastic workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Work metal and plastic in specialties not classified separately. | Set up, operate, and tend machines that form, cut, or finish metal and plastic. | Read blueprints, job orders, and specifications to determine machine settings. | Select and install dies, tooling, fixtures, and cutting tools. | Measure and inspect workpieces using calipers, micrometers, and gauges. | Adjust machine controls to maintain dimensions and surface quality. | Deburr, polish, clean, and finish parts to required standards. | Monitor machine operation and correct feed, speed, and alignment problems. | Perform routine maintenance, lubrication, and tool changes. | Record production counts, scrap, and quality data. | Follow safety procedures for machinery, chemicals, and hot materials. | Load and unload materials and stage finished parts for the next operation. | Report tooling wear, machine faults, and material defects. | Maintain a clean and organized work area and machine surroundings.</t>
+  </si>
+  <si>
+    <t>51-5111.00</t>
+  </si>
+  <si>
+    <t>Prepress Technicians and Workers</t>
+  </si>
+  <si>
+    <t>Desktop Operator | Electronic Prepress Operator (EPP Operator) | Electronic Prepress Technician (EPP Tech) | Plate Maker | Plate Mounter | Pre-Press Proofer | Prepress Operator | Prepress Specialist | Prepress Stripper | Prepress Technician</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Adobe Creative Cloud software | Adobe Director | Adobe FrameMaker | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe LifeCycle Enterprise Suite | Adobe PageMaker | Adobe Photoshop | Corel CorelDraw Graphics Suite | Corel Painter | Esko ArtPro | File transfer protocol FTP software | Global Graphics Software Harlequin | Hamrick Software VueScan | LaserSoft Imaging SilverFast Ai Studio | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Multi-line optical character reader OCR software | ProjectSend | QuarkXPress | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | English Language | Design | Mathematics | Production and Processing | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Inductive Reasoning | Visualization | Visual Color Discrimination | Category Flexibility | Information Ordering | Oral Expression | Written Comprehension | Oral Comprehension | Speech Clarity | Speech Recognition | Control Precision | Selective Attention | Perceptual Speed | Flexibility of Closure | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | E-Mail | Telephone Conversations | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Calibration Technologists and Technicians | Camera and Photographic Equipment Repairers | Computer Numerically Controlled Tool Operators | Computer Numerically Controlled Tool Programmers | Desktop Publishers | Electromechanical Equipment Assemblers | Etchers and Engravers | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Office Machine Operators, Except Computer | Painting, Coating, and Decorating Workers | Paper Goods Machine Setters, Operators, and Tenders | Patternmakers, Metal and Plastic | Photographic Process Workers and Processing Machine Operators | Print Binding and Finishing Workers | Printing Press Operators | Special Effects Artists and Animators</t>
+  </si>
+  <si>
+    <t>Format and proof text and images submitted by designers and clients into finished pages that can be printed. Includes digital and photo typesetting. May produce printing plates.</t>
+  </si>
+  <si>
+    <t>Analyze originals to evaluate color density, gradation highlights, middle tones, and shadows, using densitometers and knowledge of light and color. | Enter, position, and alter text size, using computers, to make up and arrange pages so that printed materials can be produced. | Enter, store, and retrieve information on computer-aided equipment. | Examine finished plates to detect flaws, verify conformity with master plates, and measure dot sizes and centers, using light boxes and microscopes. | Examine photographic images for obvious imperfections prior to plate making. | Examine unexposed photographic plates to detect flaws or foreign particles prior to printing. | Generate prepress proofs in digital or other format to approximate the appearance of the final printed piece. | Maintain, adjust, and clean equipment, and perform minor repairs. | Operate and maintain laser plate-making equipment that converts electronic data to plates without the use of film. | Operate presses to print proofs of plates, monitoring printing quality to ensure that it is adequate. | Perform "preflight" check of required font, graphic, text and image files to ensure completeness prior to delivery to printer. | Proofread and perform quality control of text and images. | Scale copy for reductions and enlargements, using proportion wheels. | Select proper types of plates according to press run lengths. | Set scanners to specific color densities, sizes, screen rulings, and exposure adjustments, using scanner keyboards or computers.</t>
+  </si>
+  <si>
+    <t>51-5112.00</t>
+  </si>
+  <si>
+    <t>Printing Press Operators</t>
+  </si>
+  <si>
+    <t>Digital Press Operator | Flexographic Press Operator | Offset Press Operator | Offset Pressman | Press Operator | Pressman | Printer | Printing Press Operator | Printing Pressman | Web Press Operator</t>
+  </si>
+  <si>
+    <t>AABACH Graphic Systems DIGRA | Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe LifeCycle Production Print ES3 | Adobe PageMaker | Adobe Photoshop | Corel CorelDraw Graphics Suite | Electronics for Imaging EFI Monarch | Electronics for Imaging EFI Pace | Email software | Enfocus PitStop Pro | Graphics software | Image editing software | Inventory tracking software | Job scheduling software | Job tracking software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Printers Software Inc. Presidio | Printing management system software | QuarkXPress | SAP software | Squeegee | Xerox FreeFlow Print Server | Xerox ProfitQuick</t>
+  </si>
+  <si>
+    <t>Monitoring | Reading Comprehension | Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Mechanical | Production and Processing</t>
+  </si>
+  <si>
+    <t>Near Vision | Control Precision | Problem Sensitivity | Arm-Hand Steadiness | Manual Dexterity | Speech Clarity | Speech Recognition | Multilimb Coordination | Finger Dexterity | Selective Attention | Visualization | Information Ordering | Deductive Reasoning | Oral Expression | Written Comprehension | Oral Comprehension | Perceptual Speed | Flexibility of Closure | Category Flexibility | Inductive Reasoning | Visual Color Discrimination | Far Vision | Static Strength</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Spend Time Standing | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Freedom to Make Decisions | Pace Determined by Speed of Equipment | Contact With Others | Determine Tasks, Priorities and Goals | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Walking or Running | Health and Safety of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Making Repetitive Motions | Exposed to Hazardous Equipment | Impact of Decisions on Co-workers or Company Results | Importance of Repeating Same Tasks | Exposed to Hazardous Conditions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Etchers and Engravers | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Office Machine Operators, Except Computer | Paper Goods Machine Setters, Operators, and Tenders | Photographic Process Workers and Processing Machine Operators | Prepress Technicians and Workers | Print Binding and Finishing Workers | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Textile Bleaching and Dyeing Machine Operators and Tenders | Textile Cutting Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Set up and operate digital, letterpress, lithographic, flexographic, gravure, or other printing machines. Includes short-run offset printing presses.</t>
+  </si>
+  <si>
+    <t>Adjust digital files to alter print elements, such as fonts, graphics, or color separations. | Adjust ink fountain flow rates. | Change press plates, blankets, or cylinders, as required. | Clean ink fountains, plates, or printing unit cylinders when press runs are completed. | Clean or oil presses or make minor repairs, using hand tools. | Collect and inspect random samples during print runs to identify any necessary adjustments. | Control workflow scheduling or job tracking, using computer database software. | Direct or monitor work of press crews. | Download completed jobs to archive media so that questions can be answered or jobs replicated. | Download or scan files to be printed, using printing production software. | Examine job orders to determine quantities to be printed, stock specifications, colors, or special printing instructions. | Feed paper through press cylinders and adjust feed and tension controls. | Input production job settings into workstation terminals that control automated printing systems. | Load presses with paper and make necessary adjustments, according to paper size. | Maintain time or production records. | Monitor automated press operation systems and respond to fault, error, or alert messages. | Monitor environmental factors, such as humidity and temperature, that may impact equipment performance and make necessary adjustments. | Monitor inventory levels on a regular basis, ordering or requesting additional supplies, as necessary. | Obtain or mix inks and fill ink fountains. | Secure printing plates to printing units and adjust tolerances. | Set up or operate auxiliary equipment, such as cutting, folding, plate-making, drilling, or laminating machines. | Start presses and pull proofs to check for ink coverage and density, alignment, and registration. | Verify that paper and ink meet the specifications for a given job.</t>
+  </si>
+  <si>
+    <t>51-5113.00</t>
+  </si>
+  <si>
+    <t>Print Binding and Finishing Workers</t>
+  </si>
+  <si>
+    <t>Binder Operator | Bindery Operator | Bindery Technician | Bindery Worker | Book Binder | Custom Bookbinder | Perfect Binder Operator</t>
+  </si>
+  <si>
+    <t>Email software | Houchen Bindery Library Automated Retrieval System LARS | Label printing software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Publisher | Microsoft Word | Trade Bindery Software Bindery Estimating System | Trade Bindery Software Bindery Management System | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Administration and Management | Production and Processing | Mechanical | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Near Vision | Finger Dexterity | Problem Sensitivity | Oral Expression | Oral Comprehension | Manual Dexterity | Arm-Hand Steadiness | Deductive Reasoning | Visualization | Speech Clarity | Speech Recognition | Trunk Strength | Control Precision | Selective Attention | Inductive Reasoning | Written Comprehension | Multilimb Coordination | Information Ordering</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Indoors, Environmentally Controlled | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Impact of Decisions on Co-workers or Company Results | Exposed to Hazardous Equipment | Exposed to Contaminants | Frequency of Decision Making | Importance of Repeating Same Tasks | Contact With Others | Pace Determined by Speed of Equipment | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Patternmakers, Metal and Plastic | Pressers, Textile, Garment, and Related Materials | Printing Press Operators | Sewers, Hand | Sewing Machine Operators | Shoe Machine Operators and Tenders | Textile Cutting Machine Setters, Operators, and Tenders | Textile Knitting and Weaving Machine Setters, Operators, and Tenders | Textile Winding, Twisting, and Drawing Out Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Bind books and other publications or finish printed products by hand or machine. May set up binding and finishing machines.</t>
+  </si>
+  <si>
+    <t>Bind new books, using hand tools such as bone folders, knives, hammers, or brass binding tools. | Compress sewed or glued signatures, using hand presses or smashing machines. | Cut binder boards to specified dimensions, using board shears, hand cutters, or cutting machines. | Cut cover material to specified dimensions, fitting and gluing material to binder boards by hand or machine. | Design original or special bindings for limited editions or other custom binding projects. | Examine stitched, collated, bound, or unbound product samples for defects, such as imperfect bindings, ink spots, torn pages, loose pages, or loose or uncut threads. | Form book bodies by folding and sewing printed sheets to form signatures and assembling signatures in numerical order. | Imprint or emboss lettering, designs, or numbers on book covers, using gold, silver, or colored foil, and stamping machines. | Insert book bodies in devices that form back edges of books into convex shapes and produce grooves that facilitate cover attachment. | Install or adjust bindery machine devices, such as knives, guides, rollers, rounding forms, creasing rams, or clamps, to accommodate sheets, signatures, or books of specified sizes. | Lubricate, clean, or make minor repairs to machine parts to keep machines in working condition. | Maintain records, such as daily production records, using specified forms. | Meet with clients, printers, or designers to discuss job requirements or binding plans. | Monitor machine operations to detect malfunctions or to determine whether adjustments are needed. | Perform highly skilled hand finishing binding operations, such as grooving or lettering. | Prepare finished books for shipping by wrapping or packing books and stacking boxes on pallets. | Punch holes in and fasten paper sheets, signatures, or other material, using hand or machine punches and staplers. | Read work orders to determine instructions and specifications for machine set-up. | Repair, restore, or rebind old, rare, or damaged books, using hand tools. | Set up or operate bindery machines, such as coil binders, thermal or tape binders, plastic comb binders, or specialty binders. | Set up or operate glue machines by filling glue reservoirs, turning switches to activate heating elements, or adjusting glue flow or conveyor speed. | Set up or operate machines that perform binding operations, such as pressing, folding, or trimming. | Stitch or glue endpapers, bindings, backings, or signatures, using sewing machines, glue machines, or glue and brushes. | Train workers to set up, operate, and use automatic bindery machines. | Trim edges of books to size, using cutting machines, book trimming machines, or hand cutters.</t>
+  </si>
+  <si>
+    <t>51-6011.00</t>
+  </si>
+  <si>
+    <t>Laundry and Dry-Cleaning Workers</t>
+  </si>
+  <si>
+    <t>Dry Cleaner | Laundry Aide | Laundry Assistant | Laundry Attendant | Laundry Housekeeper | Laundry Technician | Laundry Worker | Personal Clothing Laundry Aide | Spotter</t>
+  </si>
+  <si>
+    <t>Cents | Curbside Laundries Wash and Fold POS Software | Email software | Microsoft Excel | Microsoft Office software | Microsoft Windows | Microsoft Word | Property management system PMS software | Sales processing software | Wash-Dry-Fold POS | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Production and Processing</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Control Precision | Manual Dexterity | Oral Expression | Oral Comprehension | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Health and Safety of Other Workers | Spend Time Making Repetitive Motions | Pace Determined by Speed of Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Work Outcomes and Results of Other Workers | Work With or Contribute to a Work Group or Team | Spend Time Walking or Running | Indoors, Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cleaners of Vehicles and Equipment | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Dishwashers | Furniture Finishers | Grinding and Polishing Workers, Hand | Helpers--Production Workers | Janitors and Cleaners, Except Maids and Housekeeping Cleaners | Laborers and Freight, Stock, and Material Movers, Hand | Machine Feeders and Offbearers | Maids and Housekeeping Cleaners | Molders, Shapers, and Casters, Except Metal and Plastic | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Painting, Coating, and Decorating Workers | Pressers, Textile, Garment, and Related Materials | Sewing Machine Operators | Textile Bleaching and Dyeing Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Operate or tend washing or dry-cleaning machines to wash or dry-clean industrial or household articles, such as cloth garments, suede, leather, furs, blankets, draperies, linens, rugs, and carpets. Includes spotters and dyers of these articles.</t>
+  </si>
+  <si>
+    <t>Apply bleaching powders to spots and spray them with steam to remove stains from fabrics that do not respond to other cleaning solvents. | Clean machine filters, and lubricate equipment. | Determine spotting procedures and proper solvents, based on fabric and stain types. | Examine and sort into lots articles to be cleaned, according to color, fabric, dirt content, and cleaning technique required. | Hang curtains, drapes, blankets, pants, and other garments on stretch frames to dry. | Identify articles' fabrics and original dyes by sight and touch, or by testing samples with fire or chemical reagents. | Immerse articles in bleaching baths to strip colors. | Inspect soiled articles to determine sources of stains, to locate color imperfections, and to identify items requiring special treatment. | Iron or press articles, fabrics, and furs, using hand irons or pressing machines. | Load articles into washers or dry-cleaning machines, or direct other workers to perform loading. | Match sample colors, applying knowledge of bleaching agent and dye properties, and types, construction, conditions, and colors of articles. | Mix and add detergents, dyes, bleaches, starches, and other solutions and chemicals to clean, color, dry, or stiffen articles. | Mix bleaching agents with hot water in vats, and soak material until it is bleached. | Operate extractors and driers, or direct their operation. | Operate machines that comb, dry and polish furs, clean, sterilize and fluff feathers and blankets, or roll and package towels. | Pre-soak, sterilize, scrub, spot-clean, and dry contaminated or stained articles, using neutralizer solutions and portable machines. | Receive and mark articles for laundry or dry cleaning with identifying code numbers or names, using hand or machine markers. | Remove items from washers or dry-cleaning machines, or direct other workers to do so. | Sort and count articles removed from dryers, and fold, wrap, or hang them. | Spray steam, water, or air over spots to flush out chemicals, dry material, raise naps, or brighten colors. | Spread soiled articles on work tables, and position stained portions over vacuum heads or on marble slabs. | Sprinkle chemical solvents over stains, and pat areas with brushes or sponges to remove stains. | Start washers, dry cleaners, driers, or extractors, and turn valves or levers to regulate machine processes and the volume of soap, detergent, water, bleach, starch, and other additives.</t>
+  </si>
+  <si>
+    <t>51-6021.00</t>
+  </si>
+  <si>
+    <t>Pressers, Textile, Garment, and Related Materials</t>
+  </si>
+  <si>
+    <t>Boarder | Dry Cleaner Presser | Garment Presser | Ironing Machine Operator | Ironing Worker | Pants Presser | Presser | Pressing Machine Operator | Shirt Presser | Silk Presser</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Excel | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Arm-Hand Steadiness | Control Precision | Near Vision | Multilimb Coordination | Finger Dexterity | Trunk Strength | Reaction Time</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Pace Determined by Speed of Equipment | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Time Pressure | Exposed to Minor Burns, Cuts, Bites, or Stings | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding and Polishing Workers, Hand | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Molders, Shapers, and Casters, Except Metal and Plastic | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Paper Goods Machine Setters, Operators, and Tenders | Print Binding and Finishing Workers | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sewers, Hand | Sewing Machine Operators | Shoe Machine Operators and Tenders | Shoe and Leather Workers and Repairers | Tailors, Dressmakers, and Custom Sewers | Textile Bleaching and Dyeing Machine Operators and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Press or shape articles by hand or machine.</t>
+  </si>
+  <si>
+    <t>Activate and adjust machine controls to regulate temperature and pressure of rollers, ironing shoes, or plates, according to specifications. | Block or shape knitted garments after cleaning. | Brush materials made of suede, leather, or felt to remove spots or to raise and smooth naps. | Clean and maintain pressing machines, using cleaning solutions and lubricants. | Examine and measure finished articles to verify conformance to standards, using measuring devices such as tape measures and micrometers. | Finish fancy garments such as evening gowns and costumes, using hand irons to produce high quality finishes. | Finish pants, jackets, shirts, skirts and other dry-cleaned and laundered articles, using hand irons. | Finish pleated garments, determining sizes of pleats from evidence of old pleats or from work orders, using machine presses or hand irons. | Finish velvet garments by steaming them on bucks of hot-head presses or steam tables, and brushing pile (nap) with handbrushes. | Hang, fold, package, and tag finished articles for delivery to customers. | Identify and treat spots on garments. | Insert heated metal forms into ties and touch up rough places with hand irons. | Lower irons, rams, or pressing heads of machines into position over material to be pressed. | Measure fabric to specifications, cut uneven edges with shears, fold material, and press it with an iron to form a heading. | Moisten materials to soften and smooth them. | Operate steam, hydraulic, or other pressing machines to remove wrinkles from garments and flatwork items, or to shape, form, or patch articles. | Position materials such as cloth garments, felt, or straw on tables, dies, or feeding mechanisms of pressing machines, or on ironing boards or work tables. | Press ties on small pressing machines. | Push and pull irons over surfaces of articles to smooth or shape them. | Remove finished pieces from pressing machines and hang or stack them for cooling, or forward them for additional processing. | Select appropriate pressing machines, based on garment properties such as heat tolerance. | Select, install, and adjust machine components, including pressing forms, rollers, and guides, using hoists and hand tools. | Sew ends of new material to leaders or to ends of material in pressing machines, using sewing machines. | Shrink, stretch, or block articles by hand to conform to original measurements, using forms, blocks, and steam. | Slide material back and forth over heated, metal, ball-shaped forms to smooth and press portions of garments that cannot be satisfactorily pressed with flat pressers or hand irons. | Spray water over fabric to soften fibers when not using steam irons. | Straighten, smooth, or shape materials to prepare them for pressing. | Use covering cloths to prevent equipment from damaging delicate fabrics.</t>
+  </si>
+  <si>
+    <t>51-6031.00</t>
+  </si>
+  <si>
+    <t>Sewing Machine Operators</t>
+  </si>
+  <si>
+    <t>Line Closer | Machine Operator | Prototype Sewer | Sample Maker | Seamer | Seamstress | Sew On Operator | Sewer | Sewing Machine Operator | Zipper Machine Operator</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Design | English Language | Mathematics | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Control Precision | Near Vision | Finger Dexterity | Rate Control | Multilimb Coordination | Information Ordering | Visual Color Discrimination | Reaction Time | Visualization | Deductive Reasoning | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Sitting | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate | Time Pressure | Indoors, Environmentally Controlled | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Paper Goods Machine Setters, Operators, and Tenders | Pressers, Textile, Garment, and Related Materials | Print Binding and Finishing Workers | Sawing Machine Setters, Operators, and Tenders, Wood | Sewers, Hand | Shoe Machine Operators and Tenders | Shoe and Leather Workers and Repairers | Tailors, Dressmakers, and Custom Sewers | Textile Cutting Machine Setters, Operators, and Tenders | Textile Knitting and Weaving Machine Setters, Operators, and Tenders | Textile Winding, Twisting, and Drawing Out Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate or tend sewing machines to join, reinforce, decorate, or perform related sewing operations in the manufacture of garment or nongarment products.</t>
+  </si>
+  <si>
+    <t>Attach buttons, hooks, zippers, fasteners, or other accessories to fabric, using feeding hoppers or clamp holders. | Attach tape, trim, appliques, or elastic to specified garments or garment parts, according to item specifications. | Baste edges of material to align and temporarily secure parts for final assembly. | Cut excess material or thread from finished products. | Cut materials according to specifications, using blades, scissors, or electric knives. | Draw markings or pin appliques on fabric to obtain variations in design. | Examine and measure finished articles to verify conformance to standards, using rulers. | Fold or stretch edges or lengths of items while sewing to facilitate forming specified sections. | Guide garments or garment parts under machine needles and presser feet to sew parts together. | Inspect garments, and examine repair tags and markings on garments to locate defects or damage, and mark errors as necessary. | Match cloth pieces in correct sequences prior to sewing them, and verify that dye lots and patterns match. | Monitor machine operation to detect problems such as defective stitching, breaks in thread, or machine malfunctions. | Mount attachments, such as needles, cutting blades, or pattern plates, and adjust machine guides according to specifications. | Perform equipment maintenance tasks such as replacing needles, sanding rough areas of needles, or cleaning and oiling sewing machines. | Perform specialized or automatic sewing machine functions, such as buttonhole making or tacking. | Place spools of thread, cord, or other materials on spindles, insert bobbins, and thread ends through machine guides and components. | Position and mark patterns on materials to prepare for sewing. | Position items under needles, using marks on machines, clamps, templates, or cloth as guides. | Position material or articles in clamps, templates, or hoop frames prior to automatic operation of machines. | Record quantities of materials processed. | Remove holding devices and finished items from machines. | Repair or alter items by adding replacement parts or missing stitches. | Select supplies such as fasteners and thread, according to job requirements. | Start and operate or tend machines, such as single or double needle serging and flat-bed felling machines, to automatically join, reinforce, or decorate material or articles. | Tape or twist together thread or cord to repair breaks. | Turn knobs, screws, and dials to adjust settings of machines, according to garment styles and equipment performance.</t>
+  </si>
+  <si>
+    <t>51-6041.00</t>
+  </si>
+  <si>
+    <t>Shoe and Leather Workers and Repairers</t>
+  </si>
+  <si>
+    <t>Boot Maker | Cobbler | Leather Worker | Saddle and Harness Maker | Shoe Cutter | Shoe Maker | Shoe Repairer | Shoe Repairman | Stitcher</t>
+  </si>
+  <si>
+    <t>Bookkeeping software | Financial accounting software | Inventory tracking software | Microsoft Excel | Sale processing software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Finger Dexterity | Problem Sensitivity | Category Flexibility | Information Ordering | Inductive Reasoning | Deductive Reasoning | Oral Comprehension | Speech Clarity | Speech Recognition | Control Precision | Manual Dexterity | Selective Attention | Visualization</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Exposed to Hazardous Equipment | Freedom to Make Decisions | Indoors, Environmentally Controlled | Spend Time Standing | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions | Contact With Others | Importance of Being Exact or Accurate | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Time Pressure | Telephone Conversations | Frequency of Decision Making | Deal With External Customers or the Public in General</t>
+  </si>
+  <si>
+    <t>Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Etchers and Engravers | Furniture Finishers | Grinding and Polishing Workers, Hand | Jewelers and Precious Stone and Metal Workers | Medical Appliance Technicians | Molders, Shapers, and Casters, Except Metal and Plastic | Painting, Coating, and Decorating Workers | Patternmakers, Metal and Plastic | Pressers, Textile, Garment, and Related Materials | Print Binding and Finishing Workers | Sewers, Hand | Sewing Machine Operators | Shoe Machine Operators and Tenders | Stone Cutters and Carvers, Manufacturing | Tailors, Dressmakers, and Custom Sewers | Timing Device Assemblers and Adjusters | Tire Builders | Upholsterers</t>
+  </si>
+  <si>
+    <t>Construct, decorate, or repair leather and leather-like products, such as luggage, shoes, and saddles. May use hand tools.</t>
+  </si>
+  <si>
+    <t>Align and stitch or glue materials such as fabric, fleece, leather, or wood, to join parts. | Attach accessories or ornamentation to decorate or protect products. | Attach insoles to shoe lasts, affix shoe uppers, and apply heels and outsoles. | Cement, nail, or sew soles and heels to shoes. | Check the texture, color, and strength of leather to ensure that it is adequate for a particular purpose. | Clean and polish shoes. | Construct, decorate, or repair leather products according to specifications, using sewing machines, needles and thread, leather lacing, glue, clamps, hand tools, or rivets. | Cut out parts, following patterns or outlines, using knives, shears, scissors, or machine presses. | Cut, insert, position, and secure paddings, cushioning, or linings, using stitches or glue. | Draw patterns, using measurements, designs, plaster casts, or customer specifications, and position or outline patterns on work pieces. | Dress and otherwise finish boots or shoes, as by trimming the edges of new soles and heels to the shoe shape. | Drill or punch holes and insert or attach metal rings, handles, and fastening hardware, such as buckles. | Dye, soak, polish, paint, stamp, stitch, stain, buff, or engrave leather or other materials to obtain desired effects, decorations, or shapes. | Estimate the costs of requested products or services such as custom footwear or footwear repair, and receive payment from customers. | Inspect articles for defects, and remove damaged or worn parts, using hand tools. | Make, modify, and repair orthopedic or therapeutic footwear according to doctors' prescriptions, or modify existing footwear for people with foot problems and special needs. | Nail heel and toe cleats onto shoes. | Place shoes on lasts to remove soles and heels, using knives or pliers. | Prepare inserts, heel pads, and lifts from casts of customers' feet. | Re-sew seams, and replace handles and linings of suitcases or handbags. | Read prescriptions or specifications, and take measurements to establish the type of product to be made, using calipers, tape measures, or rules. | Repair and recondition leather products such as trunks, luggage, shoes, saddles, belts, purses, and baseball gloves. | Repair or replace soles, heels, and other parts of footwear, using sewing, buffing and other shoe repair machines, materials, and equipment. | Select materials and patterns, and trace patterns onto materials to be cut out. | Shape shoe heels with a knife, and sand them on a buffing wheel for smoothness. | Stretch shoes, dampening parts and inserting and twisting parts, using an adjustable stretcher.</t>
+  </si>
+  <si>
+    <t>51-6042.00</t>
+  </si>
+  <si>
+    <t>Shoe Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Boot Maker | Cobbler | Inseamer | Insole Department Worker | Shoe Cementer | Shoe Maker | Side Laster | Stitcher | Toe Trimmer</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Production control software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Monitoring</t>
+  </si>
+  <si>
+    <t>Production and Processing | Administration and Management</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Control Precision | Finger Dexterity | Manual Dexterity | Perceptual Speed | Problem Sensitivity | Oral Expression | Reaction Time | Multilimb Coordination | Selective Attention | Extent Flexibility</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Repeating Same Tasks | Indoors, Environmentally Controlled | Pace Determined by Speed of Equipment | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Molders, Shapers, and Casters, Except Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Pressers, Textile, Garment, and Related Materials | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sawing Machine Setters, Operators, and Tenders, Wood | Sewers, Hand | Sewing Machine Operators | Shoe and Leather Workers and Repairers | Textile Cutting Machine Setters, Operators, and Tenders | Textile Winding, Twisting, and Drawing Out Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate or tend a variety of machines to join, decorate, reinforce, or finish shoes and shoe parts.</t>
+  </si>
+  <si>
+    <t>Align parts to be stitched, following seams, edges, or markings, before positioning them under needles. | Collect shoe parts from conveyer belts or racks and place them in machinery such as ovens or on molds for dressing, returning them to conveyers or racks to send them to the next work station. | Cut excess thread or material from shoe parts, using scissors or knives. | Draw thread through machine guide slots, needles, and presser feet in preparation for stitching, or load rolls of wire through machine axles. | Fill shuttle spools with thread from a machine's bobbin winder by pressing a foot treadle. | Hammer loose staples for proper attachment. | Inspect finished products to ensure that shoes have been completed according to specifications. | Operate or tend machines to join, decorate, reinforce, or finish shoes and shoe parts. | Perform routine equipment maintenance such as cleaning and lubricating machines or replacing broken needles. | Position dies on material in a manner that will obtain the maximum number of parts from each portion of material. | Remove and examine shoes, shoe parts, and designs to verify conformance to specifications such as proper embedding of stitches in channels. | Select and place spools of thread or pre-wound bobbins into shuttles, or onto spindles or loupers of stitching machines. | Staple sides of shoes, pressing a foot treadle to position and hold each shoe under the feeder of the machine. | Study work orders or shoe part tags to obtain information about workloads, specifications, and the types of materials to be used. | Switch on machines, lower pressure feet or rollers to secure parts, and start machine stitching, using hand, foot, or knee controls. | Test machinery to ensure proper functioning before beginning production. | Turn knobs to adjust stitch length and thread tension. | Turn screws to regulate size of staples. | Turn setscrews on needle bars, and position required numbers of needles in stitching machines.</t>
+  </si>
+  <si>
+    <t>51-6051.00</t>
+  </si>
+  <si>
+    <t>Sewers, Hand</t>
+  </si>
+  <si>
+    <t>Alteration Specialist | Couturier | Custom Clothier | Custom Designer | Custom Seamstress | Seamstress | Stitcher</t>
+  </si>
+  <si>
+    <t>Adobe FreeHand MX | Adobe Illustrator | Adobe Photoshop | Corel CorelDraw Graphics Suite | Drawing software | Embroidery design software | Graphics digitizing software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Template design software</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Near Vision | Control Precision | Visualization | Category Flexibility | Information Ordering | Visual Color Discrimination | Multilimb Coordination</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Pace Determined by Speed of Equipment | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Fabric and Apparel Patternmakers | Furniture Finishers | Grinding and Polishing Workers, Hand | Jewelers and Precious Stone and Metal Workers | Laundry and Dry-Cleaning Workers | Molders, Shapers, and Casters, Except Metal and Plastic | Painting, Coating, and Decorating Workers | Patternmakers, Metal and Plastic | Pressers, Textile, Garment, and Related Materials | Print Binding and Finishing Workers | Sewing Machine Operators | Shoe Machine Operators and Tenders | Shoe and Leather Workers and Repairers | Structural Metal Fabricators and Fitters | Tailors, Dressmakers, and Custom Sewers | Textile Knitting and Weaving Machine Setters, Operators, and Tenders | Upholsterers</t>
+  </si>
+  <si>
+    <t>Sew, join, reinforce, or finish, usually with needle and thread, a variety of manufactured items. Includes weavers and stitchers.</t>
+  </si>
+  <si>
+    <t>Draw and cut patterns according to specifications. | Fit garments on clients, altering as needed. | Fold, twist, stretch, or drape material, and secure articles in preparation for sewing. | Measure and align parts, fasteners, or trimmings, following seams, edges, or markings on parts. | Select thread, twine, cord, or yarn to be used, and thread needles. | Sew buttonholes, or add lace or other trimming. | Sew, join, reinforce, or finish parts of articles, such as garments, books, mattresses, toys, and wigs, using needles and thread or other materials. | Smooth seams with heated irons, flat bones, or rubbing sticks. | Tie, knit, weave or knot ribbon, yarn, or decorative materials. | Trim excess threads or edges of parts, using scissors or knives. | Use different sewing techniques such as felling, tacking, basting, embroidery, and fagoting.</t>
+  </si>
+  <si>
+    <t>51-6052.00</t>
+  </si>
+  <si>
+    <t>Tailors, Dressmakers, and Custom Sewers</t>
+  </si>
+  <si>
+    <t>Alterations Expert | Alterations Sewer | Bridal Designer | Clothing Pattern Designer | Custom Dressmaker | Custom Sewer | Custom Tailor | Dressmaker | Seamstress | Tailor</t>
+  </si>
+  <si>
+    <t>ArbelSoft TailorMax | Bookkeeping software | Garment design software | Google Docs | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft Word | Tailor Master</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Production and Processing | Administration and Management | Economics and Accounting</t>
+  </si>
+  <si>
+    <t>Visualization | Arm-Hand Steadiness | Finger Dexterity | Near Vision | Oral Comprehension | Control Precision | Manual Dexterity | Information Ordering | Originality | Oral Expression | Speech Clarity | Speech Recognition | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Importance of Being Exact or Accurate | Freedom to Make Decisions | Indoors, Environmentally Controlled | Impact of Decisions on Co-workers or Company Results | Telephone Conversations | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Spend Time Sitting | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Pace Determined by Speed of Equipment | Work With or Contribute to a Work Group or Team | Physical Proximity | Spend Time Making Repetitive Motions | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Fabric and Apparel Patternmakers | Fashion Designers | Jewelers and Precious Stone and Metal Workers | Laundry and Dry-Cleaning Workers | Layout Workers, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Painting, Coating, and Decorating Workers | Patternmakers, Metal and Plastic | Patternmakers, Wood | Pressers, Textile, Garment, and Related Materials | Print Binding and Finishing Workers | Sewers, Hand | Sewing Machine Operators | Shoe Machine Operators and Tenders | Shoe and Leather Workers and Repairers | Textile Bleaching and Dyeing Machine Operators and Tenders | Textile Knitting and Weaving Machine Setters, Operators, and Tenders | Upholsterers</t>
+  </si>
+  <si>
+    <t>Design, make, alter, repair, or fit garments.</t>
+  </si>
+  <si>
+    <t>Assemble garment parts and join parts with basting stitches, using needles and thread or sewing machines. | Confer with customers to determine types of material and garment styles desired. | Develop, copy, or adapt designs for garments, and design patterns to fit measurements, applying knowledge of garment design, construction, styling, and fabric. | Estimate how much a garment will cost to make, based on factors such as time and material requirements. | Examine tags on garments to determine alterations that are needed. | Fit and study garments on customers to determine required alterations. | Fit, alter, repair, and make made-to-measure clothing, according to customers' and clothing manufacturers' specifications and fit, and applying principles of garment design, construction, and styling. | Let out or take in seams in suits and other garments to improve fit. | Maintain garment drape and proportions as alterations are performed. | Make garment style changes, such as tapering pant legs, narrowing lapels, and adding or removing padding. | Measure customers, using tape measures, and record measurements. | Measure parts, such as sleeves or pant legs, and mark or pin-fold alteration lines. | Position patterns of garment parts on fabric, and cut fabric along outlines, using scissors. | Press garments, using hand irons or pressing machines. | Put in padding and shaping materials. | Record required alterations and instructions on tags, and attach them to garments. | Remove stitches from garments to be altered, using rippers or razor blades. | Repair or replace defective garment parts, such as pockets, zippers, snaps, buttons, and linings. | Sew buttonholes and attach buttons to finish garments. | Sew garments, using needles and thread or sewing machines. | Take up or let down hems to shorten or lengthen garment parts, such as sleeves. | Trim excess material, using scissors.</t>
+  </si>
+  <si>
+    <t>51-6061.00</t>
+  </si>
+  <si>
+    <t>Textile Bleaching and Dyeing Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Beck Operator | Dye House Worker | Dye Line Operator | Dye Machine Operator | Dye Operator | Dye Tub Operator | Dyer | Jet Dyeing Machine Operator | Machine Operator (Machine Op) | Tub Operator</t>
+  </si>
+  <si>
+    <t>Hewlett-Packard HP OpenVMS | Linux | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Control Precision | Near Vision | Visual Color Discrimination | Manual Dexterity | Rate Control | Finger Dexterity | Selective Attention | Perceptual Speed | Information Ordering | Deductive Reasoning | Oral Comprehension | Speech Recognition | Far Vision | Trunk Strength | Static Strength | Reaction Time | Visualization | Flexibility of Closure | Category Flexibility | Inductive Reasoning | Problem Sensitivity | Oral Expression</t>
+  </si>
+  <si>
+    <t>Exposed to Contaminants | Spend Time Standing | Indoors, Not Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Pace Determined by Speed of Equipment | Importance of Being Exact or Accurate | Contact With Others | Spend Time Walking or Running | Exposed to Very Hot or Cold Temperatures | Work With or Contribute to a Work Group or Team | Exposed to Hazardous Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Exposed to Hazardous Equipment | Frequency of Decision Making | Time Pressure | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Mixing and Blending Machine Setters, Operators, and Tenders | Packaging and Filling Machine Operators and Tenders | Paper Goods Machine Setters, Operators, and Tenders | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Sewing Machine Operators | Textile Cutting Machine Setters, Operators, and Tenders | Textile Knitting and Weaving Machine Setters, Operators, and Tenders | Textile Winding, Twisting, and Drawing Out Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Operate or tend machines to bleach, shrink, wash, dye, or finish textiles or synthetic or glass fibers.</t>
+  </si>
+  <si>
+    <t>Add dyes, water, detergents, or chemicals to tanks to dilute or strengthen solutions, according to established formulas and solution test results. | Adjust equipment controls to maintain specified heat, tension, and speed. | Confer with coworkers to get information about order details, processing plans, or problems that occur. | Examine and feel products to identify defects and variations from coloring and other processing standards. | Inspect machinery to determine necessary adjustments and repairs. | Install, level, and align components such as gears, chains, dies, cutters, and needles. | Key in processing instructions to program electronic equipment. | Monitor factors such as temperatures and dye flow rates to ensure that they are within specified ranges. | Mount rolls of cloth on machines, using hoists, or place textile goods in machines or pieces of equipment. | Notify supervisors or mechanics of equipment malfunctions. | Observe display screens, control panels, equipment, and cloth entering or exiting processes to determine if equipment is operating correctly. | Perform machine maintenance, such as cleaning and oiling equipment, and repair or replace worn or defective parts. | Prepare dyeing machines for production runs, and conduct test runs of machines to ensure their proper operation. | Ravel seams that connect cloth ends when processing is completed. | Record production information such as fabric yardage processed, temperature readings, fabric tensions, and machine speeds. | Remove dyed articles from tanks and machines for drying and further processing. | Sew ends of cloth together, by hand or using machines, to form endless lengths of cloth to facilitate processing. | Soak specified textile products for designated times. | Start and control machines and equipment to wash, bleach, dye, or otherwise process and finish fabric, yarn, thread, or other textile goods. | Study guides, charts, and specification sheets, and confer with supervisors to determine machine setup requirements. | Test solutions used to process textile goods to detect variations from standards. | Thread ends of cloth or twine through specified sections of equipment prior to processing. | Weigh ingredients, such as dye, to be mixed together for use in textile processing.</t>
+  </si>
+  <si>
+    <t>51-6062.00</t>
+  </si>
+  <si>
+    <t>Textile Cutting Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Automated Cutting Machine Operator | CNC Cutting Operator (Computer Numerical Control Cutting Operator) | Cutter | Cutter Operator | Die Cut Operator | Fabric Cutter | Laser Operator | Spread Cutter | Spreader | Textile Slitting Machine Operator</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | HAISEN SoftWare System | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Information Ordering | Manual Dexterity | Auditory Attention | Near Vision | Trunk Strength | Static Strength | Reaction Time | Multilimb Coordination | Control Precision | Finger Dexterity | Selective Attention | Problem Sensitivity | Perceptual Speed | Category Flexibility | Deductive Reasoning | Oral Expression | Oral Comprehension | Visualization | Speech Clarity | Depth Perception | Rate Control | Response Orientation</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Pace Determined by Speed of Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Time Pressure | Indoors, Not Environmentally Controlled | Exposed to Contaminants | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Exposed to Hazardous Equipment</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sawing Machine Setters, Operators, and Tenders, Wood | Sewing Machine Operators | Shoe Machine Operators and Tenders | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines that cut textiles.</t>
+  </si>
+  <si>
+    <t>Adjust cutting techniques to types of fabrics and styles of garments. | Adjust machine controls, such as heating mechanisms, tensions, or speeds, to produce specified products. | Clean, oil, and lubricate machines, using air hoses, cleaning solutions, rags, oilcans, and grease guns. | Confer with coworkers to obtain information about orders, processes, or problems. | Inspect machinery to determine whether repairs are needed. | Inspect products to ensure that the quality standards and specifications are met. | Install, level, and align components, such as gears, chains, guides, dies, cutters, or needles, to set up machinery for operation. | Notify supervisors of mechanical malfunctions. | Operate machines for test runs to verify adjustments and to obtain product samples. | Operate machines to cut multiple layers of fabric into parts for articles such as canvas goods, house furnishings, garments, hats, or stuffed toys. | Place patterns on top of layers of fabric and cut fabric following patterns, using electric or manual knives, cutters, or computer numerically controlled cutting devices. | Program electronic equipment. | Record information about work completed and machine settings. | Repair or replace worn or defective parts or components, using hand tools. | Start machines, monitor operations, and make adjustments as needed. | Stop machines when specified amounts of product have been produced. | Study guides, samples, charts, and specification sheets or confer with supervisors or engineering staff to determine set-up requirements. | Thread yarn, thread, or fabric through guides, needles, and rollers of machines.</t>
+  </si>
+  <si>
+    <t>51-6063.00</t>
+  </si>
+  <si>
+    <t>Textile Knitting and Weaving Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Knitter | Knitting Machine Operator | Loom Fixer | Machine Operator | Operator | Tufting Machine Operator | Tufting Operator | Warp Knit Operator | Weaver | Winder Operator</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Production and Processing | English Language</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Finger Dexterity | Control Precision | Multilimb Coordination | Manual Dexterity | Trunk Strength | Near Vision | Selective Attention | Problem Sensitivity | Oral Comprehension | Auditory Attention | Reaction Time | Visualization | Oral Expression</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Pace Determined by Speed of Equipment | Time Pressure | Spend Time Standing | Importance of Being Exact or Accurate | Spend Time Walking or Running | Freedom to Make Decisions | Contact With Others | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Health and Safety of Other Workers | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Machine Feeders and Offbearers | Paper Goods Machine Setters, Operators, and Tenders | Print Binding and Finishing Workers | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sewers, Hand | Sewing Machine Operators | Shoe Machine Operators and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders | Textile Cutting Machine Setters, Operators, and Tenders | Textile Winding, Twisting, and Drawing Out Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines that knit, loop, weave, or draw in textiles.</t>
+  </si>
+  <si>
+    <t>Adjust machine heating mechanisms, tensions, and speeds to produce specified products. | Clean, oil, and lubricate machines, using air hoses, cleaning solutions, rags, oil cans, or grease guns. | Confer with co-workers to obtain information about orders, processes, or problems. | Examine looms to determine causes of loom stoppage, such as warp filling, harness breaks, or mechanical defects. | Inspect machinery to determine whether repairs are needed. | Inspect products to ensure that specifications are met and to determine if machines need adjustment. | Install, level, and align machine components such as gears, chains, guides, dies, cutters, or needles to set up machinery for operation. | Notify supervisors or repair staff of mechanical malfunctions. | Observe woven cloth to detect weaving defects. | Operate machines for test runs to verify adjustments and to obtain product samples. | Program electronic equipment. | Record information about work completed and machine settings. | Remove defects in cloth by cutting and pulling out filling. | Repair or replace worn or defective needles and other components, using hand tools. | Set up, or set up and operate textile machines that perform textile processing and manufacturing operations such as winding, twisting, knitting, weaving, bonding, or stretching. | Start machines, monitor operations, and make adjustments as needed. | Stop machines when specified amounts of product have been produced. | Study guides, loom patterns, samples, charts, or specification sheets, or confer with supervisors or engineering staff to determine setup requirements. | Thread yarn, thread, and fabric through guides, needles, and rollers of machines for weaving, knitting, or other processing.</t>
+  </si>
+  <si>
+    <t>51-6064.00</t>
+  </si>
+  <si>
+    <t>Textile Winding, Twisting, and Drawing Out Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Back Winder | Cable Operator | Computer Integrated Manufacturing Operator (CIM Operator) | Drawing Operator | Line Operator | Spinner | Spinning Operator | Twister Operator | Winder Operator | Winder Tender</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Speaking | Monitoring | Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Administration and Management | Mechanical | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Control Precision | Finger Dexterity | Manual Dexterity | Reaction Time | Multilimb Coordination | Trunk Strength | Near Vision | Extent Flexibility | Static Strength | Selective Attention | Problem Sensitivity | Visualization | Perceptual Speed | Flexibility of Closure | Category Flexibility | Oral Expression | Speech Clarity | Auditory Attention | Visual Color Discrimination | Far Vision | Wrist-Finger Speed | Rate Control</t>
+  </si>
+  <si>
+    <t>Spend Time Walking or Running | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Pace Determined by Speed of Equipment | Spend Time Making Repetitive Motions | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Coil Winders, Tapers, and Finishers | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sewing Machine Operators | Shoe Machine Operators and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders | Textile Cutting Machine Setters, Operators, and Tenders | Textile Knitting and Weaving Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines that wind or twist textiles; or draw out and combine sliver, such as wool, hemp, or synthetic fibers. Includes slubber machine and drawing frame operators.</t>
+  </si>
+  <si>
+    <t>Adjust machine settings such as speed or tension to produce products that meet specifications. | Clean, oil, and lubricate machines, using air hoses, cleaning solutions, rags, oilcans, and grease guns. | Inspect machinery to determine whether repairs are needed. | Inspect products to verify that they meet specifications and to determine whether machine adjustment is needed. | Install, level, and align machine components such as gears, chains, guides, dies, cutters, or needles to set up machinery for operation. | Measure bobbins periodically, using gauges, and turn screws to adjust tension if bobbins are not of specified size. | Notify supervisors or mechanics of equipment malfunctions. | Observe bobbins as they are winding and cut threads to remove loaded bobbins, using knives. | Observe operations to detect defects, malfunctions, or supply shortages. | Operate machines for test runs to verify adjustments and to obtain product samples. | Place bobbins on spindles and insert spindles into bobbin-winding machines. | Record production data such as numbers and types of bobbins wound. | Remove spindles from machines and bobbins from spindles. | Repair or replace worn or defective parts or components, using hand tools. | Replace depleted supply packages with full packages. | Start machines, monitor operation, and make adjustments as needed. | Stop machines when specified amount of products has been produced. | Study guides, samples, charts, and specification sheets, or confer with supervisors or engineering staff to determine setup requirements. | Tend machines that twist together two or more strands of yarn or insert additional twists into single strands of yarn to increase strength, smoothness, or uniformity of yarn. | Tend machines with multiple winding units that wind thread onto shuttle bobbins for use on sewing machines or other kinds of bobbins for sole-stitching, knitting, or weaving machinery. | Tend spinning frames that draw out and twist roving or sliver into yarn. | Thread yarn, thread, or fabric through guides, needles, and rollers of machines. | Unwind lengths of yarn, thread, or twine from spools and wind onto bobbins.</t>
+  </si>
+  <si>
+    <t>51-6091.00</t>
+  </si>
+  <si>
+    <t>Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers</t>
+  </si>
+  <si>
+    <t>Extruder | Extruder Operator | Extrusion Line Operator | Extrusion Operator | Granulator | Hot End Operator | Pelletizer Operator | Pot Tipper | Spindraw Operator | Stretch Operator</t>
+  </si>
+  <si>
+    <t>Apache Hadoop YARN | Camstar Manufacturing Execution System MES | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Operational databases | SAP software | Statistical process control SPC software</t>
+  </si>
+  <si>
+    <t>Production and Processing | English Language | Mathematics | Education and Training | Mechanical</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Control Precision | Near Vision | Finger Dexterity | Arm-Hand Steadiness | Oral Comprehension | Manual Dexterity | Multilimb Coordination | Reaction Time | Rate Control | Information Ordering | Inductive Reasoning | Deductive Reasoning | Oral Expression | Trunk Strength | Time Sharing | Selective Attention | Visualization | Perceptual Speed | Flexibility of Closure | Category Flexibility | Written Comprehension | Speech Clarity | Auditory Attention</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Contact With Others | Exposed to Very Hot or Cold Temperatures | Frequency of Decision Making | Importance of Being Exact or Accurate | Telephone Conversations | Impact of Decisions on Co-workers or Company Results | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Health and Safety of Other Workers | Consequence of Error | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | E-Mail | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Pace Determined by Speed of Equipment</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Coil Winders, Tapers, and Finishers | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Textile Bleaching and Dyeing Machine Operators and Tenders | Textile Cutting Machine Setters, Operators, and Tenders | Textile Winding, Twisting, and Drawing Out Machine Setters, Operators, and Tenders | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines that extrude and form continuous filaments from synthetic materials, such as liquid polymer, rayon, and fiberglass.</t>
+  </si>
+  <si>
+    <t>Clean and maintain extruding and forming machines, using hand tools. | Load materials into extruding and forming machines, using hand tools, and adjust feed mechanisms to set feed rates. | Lower pans inside cabinets to catch molten filaments until flow of polymer through packs has stopped. | Move controls to activate and adjust extruding and forming machines. | Notify other workers of defects, and direct them to adjust extruding and forming machines. | Observe flow of finish across finish rollers, and turn valves to adjust flow to specifications. | Observe machine operations, control boards, and gauges to detect malfunctions such as clogged bushings and defective binder applicators. | Open cabinet doors to cut multifilament threadlines away from guides, using scissors. | Press buttons to stop machines when processes are complete or when malfunctions are detected. | Press metering-pump buttons and turn valves to stop flow of polymers. | Record details of machine malfunctions. | Record operational data on tags, and attach tags to machines. | Remove excess, entangled, or completed filaments from machines, using hand tools. | Remove polymer deposits from spinnerettes and equipment, using silicone spray, brass chisels, and bronze-wool pads. | Set up, operate, or tend machines that extrude and form filaments from synthetic materials such as rayon, fiberglass, or liquid polymers. | Start metering pumps and observe operation of machines and equipment to ensure continuous flow of filaments extruded through spinnerettes and to detect processing defects. | Wipe finish rollers with cloths and wash finish trays with water when necessary.</t>
+  </si>
+  <si>
+    <t>51-6092.00</t>
+  </si>
+  <si>
+    <t>Fabric and Apparel Patternmakers</t>
+  </si>
+  <si>
+    <t>Cutter | Designer | Fabric Cutter | Pattern Designer | Pattern Maker | Pattern Technician | Production Pattern Maker | Sewing Pattern Layout Technician | Technical Designer</t>
+  </si>
+  <si>
+    <t>Adobe Creative Cloud software | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Gerber Technology AccuMark | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | PatternMaker</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Reading Comprehension | Speaking | Mathematics | Active Learning | Monitoring | Learning Strategies | Writing</t>
+  </si>
+  <si>
+    <t>Design | Mathematics | English Language | Production and Processing | Education and Training</t>
+  </si>
+  <si>
+    <t>Visualization | Near Vision | Originality | Information Ordering | Deductive Reasoning | Mathematical Reasoning | Written Comprehension | Oral Expression | Finger Dexterity | Number Facility | Oral Comprehension | Category Flexibility | Inductive Reasoning | Perceptual Speed | Selective Attention | Fluency of Ideas | Problem Sensitivity | Speech Clarity | Speech Recognition | Far Vision | Manual Dexterity | Arm-Hand Steadiness | Flexibility of Closure | Written Expression | Visual Color Discrimination | Control Precision | Time Sharing</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Contact With Others | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Time Pressure | Telephone Conversations | Indoors, Environmentally Controlled | Impact of Decisions on Co-workers or Company Results | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | E-Mail | Spend Time Making Repetitive Motions | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Commercial and Industrial Designers | Craft Artists | Cutters and Trimmers, Hand | Etchers and Engravers | Fashion Designers | Layout Workers, Metal and Plastic | Model Makers, Metal and Plastic | Model Makers, Wood | Molders, Shapers, and Casters, Except Metal and Plastic | Painting, Coating, and Decorating Workers | Patternmakers, Metal and Plastic | Patternmakers, Wood | Sewers, Hand | Sewing Machine Operators | Shoe Machine Operators and Tenders | Shoe and Leather Workers and Repairers | Stone Cutters and Carvers, Manufacturing | Tailors, Dressmakers, and Custom Sewers | Textile Cutting Machine Setters, Operators, and Tenders | Tool and Die Makers</t>
+  </si>
+  <si>
+    <t>Draw and construct sets of precision master fabric patterns or layouts. May also mark and cut fabrics and apparel.</t>
+  </si>
+  <si>
+    <t>Compute dimensions of patterns according to sizes, considering stretching of material. | Create a master pattern for each size within a range of garment sizes, using charts, drafting instruments, computers, or grading devices. | Create a paper pattern from which to mass-produce a design concept. | Create design specifications to provide instructions on garment sewing and assembly. | Determine the best layout of pattern pieces to minimize waste of material, and mark fabric accordingly. | Discuss design specifications with designers, and convert their original models of garments into patterns of separate parts that can be laid out on a length of fabric. | Draw details on outlined parts to indicate where parts are to be joined, as well as the positions of pleats, pockets, buttonholes, and other features, using computers or drafting instruments. | Draw outlines of pattern parts by adapting or copying existing patterns, or by drafting new patterns. | Examine sketches, sample articles, and design specifications to determine quantities, shapes, and sizes of pattern parts, and to determine the amount of material or fabric required to make a product. | Input specifications into computers to assist with pattern design and pattern cutting. | Make adjustments to patterns after fittings. | Mark samples and finished patterns with information, such as garment size, section, style, identification, and sewing instructions. | Position and cut out master or sample patterns, using scissors and knives, or print out copies of patterns, using computers. | Test patterns by making and fitting sample garments. | Trace outlines of paper onto cardboard patterns, and cut patterns into parts to make templates. | Trace outlines of specified patterns onto material, and cut fabric, using scissors.</t>
+  </si>
+  <si>
+    <t>51-6093.00</t>
+  </si>
+  <si>
+    <t>Upholsterers</t>
+  </si>
+  <si>
+    <t>Box Spring Upholsterer | Furniture Upholsterer | Inside Upholsterer | Sofa Back Upholsterer | Stapler | Trimmer | Upholstered Goods Crafter | Upholsterer | Upholstery Cutter | Upholstery Trimmer</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Intuit QuickBooks | LibreOffice Draw | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Windows | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Monitoring | Active Learning | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Design</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Near Vision | Control Precision | Multilimb Coordination | Visual Color Discrimination | Visualization | Written Comprehension | Problem Sensitivity | Extent Flexibility | Trunk Strength | Information Ordering | Static Strength | Selective Attention | Flexibility of Closure | Category Flexibility | Deductive Reasoning | Originality | Oral Expression | Oral Comprehension | Speech Clarity | Depth Perception</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Importance of Being Exact or Accurate | Spend Time Making Repetitive Motions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Spend Time Bending or Twisting Your Body | Face-to-Face Discussions with Individuals and Within Teams | Level of Competition | Determine Tasks, Priorities and Goals | Contact With Others | Indoors, Environmentally Controlled | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Body and Related Repairers | Cabinetmakers and Bench Carpenters | Carpenters | Carpet Installers | Cutters and Trimmers, Hand | Fiberglass Laminators and Fabricators | Furniture Finishers | Grinding and Polishing Workers, Hand | Layout Workers, Metal and Plastic | Model Makers, Wood | Molders, Shapers, and Casters, Except Metal and Plastic | Painting, Coating, and Decorating Workers | Sewers, Hand | Sewing Machine Operators | Shoe Machine Operators and Tenders | Shoe and Leather Workers and Repairers | Stone Cutters and Carvers, Manufacturing | Structural Metal Fabricators and Fitters | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Make, repair, or replace upholstery for household furniture or transportation vehicles.</t>
+  </si>
+  <si>
+    <t>Adjust or replace webbing, padding, or springs, and secure them in place. | Attach bindings or apply solutions to edges of cut material to prevent raveling. | Attach fasteners, grommets, buttons, buckles, ornamental trim, and other accessories to covers or frames, using hand tools. | Build furniture up with loose fiber stuffing, cotton, felt, or foam padding to form smooth, rounded surfaces. | Collaborate with interior designers to decorate rooms and coordinate furnishing fabrics. | Design upholstery cover patterns and cutting plans, based on sketches, customer descriptions, or blueprints. | Discuss upholstery fabrics, colors, and styles with customers, and provide cost estimates. | Draw cutting lines on material following patterns, templates, sketches, or blueprints, using chalk, pencils, paint, or other methods. | Examine furniture frames, upholstery, springs, and webbing to locate defects. | Fit, install, and secure material on frames, using hand tools, power tools, glue, cement, or staples. | Interweave and fasten strips of webbing to the backs and undersides of furniture, using small hand tools and fasteners. | Maintain records of time required to perform each job. | Make, repair, or replace automobile upholstery and convertible and vinyl tops, using knowledge of fabric and upholstery methods. | Make, restore, or create custom upholstered furniture, using hand tools and knowledge of fabrics and upholstery methods. | Measure and cut new covering materials, using patterns and measuring and cutting instruments, following sketches and design specifications. | Operate sewing machines or sew upholstery by hand to seam cushions and join various sections of covering material. | Pick up and deliver furniture. | Read work orders, and apply knowledge and experience with materials to determine types and amounts of materials required to cover workpieces. | Remove covering, webbing, padding, or defective springs from workpieces, using hand tools such as hammers and tack pullers. | Repair furniture frames and refinish exposed wood. | Sew rips or tears in material, or create tufting, using needles and thread. | Stretch webbing and fabric, using webbing stretchers.</t>
+  </si>
+  <si>
+    <t>51-6099.00</t>
+  </si>
+  <si>
+    <t>Textile, Apparel, and Furnishings Workers, All Other</t>
+  </si>
+  <si>
+    <t>Apparel Worker | Fabric Worker | Furnishings Worker | Garment Worker | Leather Worker | Textile Worker | Trimmer | Upholstery Worker | Sewing Operator | Textile Production Worker</t>
+  </si>
+  <si>
+    <t>Supervisory control and data acquisition SCADA software | Programmable logic controller PLC software | Statistical process control SPC software | Materials requirement planning MRP software | Computerized maintenance management system CMMS | Microsoft Excel | Microsoft Word | Email software | Inventory management systems | Enterprise resource planning ERP system | Database software | SAP software | Adobe Illustrator</t>
+  </si>
+  <si>
+    <t>Production and Processing | Design | Mechanical | English Language | Mathematics | Customer and Personal Service | Chemistry</t>
+  </si>
+  <si>
+    <t>Sewing Machine Operators | Sewers, Hand | Tailors, Dressmakers, and Custom Sewers | Upholsterers | Shoe and Leather Workers and Repairers | Shoe Machine Operators and Tenders | Pressers, Textile, Garment, and Related Materials | Laundry and Dry-Cleaning Workers | Textile Cutting Machine Setters, Operators, and Tenders | Textile Knitting and Weaving Machine Setters, Operators, and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders | Textile Winding, Twisting, and Drawing Out Machine Setters, Operators, and Tenders | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Fabric and Apparel Patternmakers | Cutters and Trimmers, Hand | Inspectors, Testers, Sorters, Samplers, and Weighers | Fashion Designers | First-Line Supervisors of Production and Operating Workers | Helpers--Production Workers | Production Workers, All Other</t>
+  </si>
+  <si>
+    <t>All textile, apparel, and furnishings workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Produce textile, apparel, and furnishings products in roles not classified separately. | Cut, sew, join, and finish fabrics, leather, and related materials. | Operate sewing, cutting, pressing, and finishing machines. | Read patterns, work tickets, and specifications to determine operations. | Measure and mark materials for cutting and assembly. | Inspect materials and finished goods for flaws, sizing, and workmanship. | Trim, clean, and repair defects in products before final inspection. | Adjust machine tension, needles, and settings for different materials. | Perform routine cleaning, oiling, and minor repair of machines. | Record production counts, defects, and material usage. | Attach labels, fasteners, trim, and decorative elements. | Package, fold, and prepare finished products for shipment. | Follow safety procedures for cutting tools, presses, and chemicals. | Maintain organized work areas and material supplies.</t>
+  </si>
+  <si>
+    <t>51-7011.00</t>
+  </si>
+  <si>
+    <t>Cabinetmakers and Bench Carpenters</t>
+  </si>
+  <si>
+    <t>Cabinet Assembler | Cabinet Builder | Cabinet Installer | Cabinetmaker | Double End Tenon Operator | Frame Builder | Framer | Woodworker</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Computer estimation software | Computerized maintenance management system CMMS | Microsoft Excel | Microsoft Outlook | Microsoft Windows</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Mathematics | Building and Construction | Production and Processing | Mechanical | Design | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Near Vision | Control Precision | Multilimb Coordination | Trunk Strength | Visualization | Reaction Time | Static Strength | Problem Sensitivity | Information Ordering | Deductive Reasoning | Written Comprehension | Selective Attention | Perceptual Speed | Category Flexibility | Inductive Reasoning | Oral Expression | Oral Comprehension | Hearing Sensitivity | Depth Perception | Far Vision | Extent Flexibility | Response Orientation | Speech Recognition | Auditory Attention</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Indoors, Not Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Equipment | Importance of Being Exact or Accurate | Time Pressure | Contact With Others | Work With or Contribute to a Work Group or Team | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Frequency of Decision Making | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Carpenters | Furniture Finishers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Helpers--Carpenters | Layout Workers, Metal and Plastic | Model Makers, Metal and Plastic | Model Makers, Wood | Molders, Shapers, and Casters, Except Metal and Plastic | Patternmakers, Metal and Plastic | Patternmakers, Wood | Sawing Machine Setters, Operators, and Tenders, Wood | Sheet Metal Workers | Stone Cutters and Carvers, Manufacturing | Structural Metal Fabricators and Fitters | Tool and Die Makers | Upholsterers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Cut, shape, and assemble wooden articles or set up and operate a variety of woodworking machines, such as power saws, jointers, and mortisers to surface, cut, or shape lumber or to fabricate parts for wood products.</t>
+  </si>
+  <si>
+    <t>Apply Masonite, formica, or vinyl surfacing materials. | Attach parts or subassemblies together to form completed units, using glue, dowels, nails, screws, or clamps. | Bore holes for insertion of screws or dowels, by hand or using boring machines. | Cut timber to the right size, and shape and trim parts of joints to ensure a snug fit, using hand tools, such as planes, chisels, or wood files. | Design furniture, using computer-aided drawing programs. | Dip, brush, or spray assembled articles with protective or decorative finishes, such as stain, varnish, paint, or lacquer. | Draw up detailed specifications and discuss projects with customers. | Establish the specifications of articles to be constructed or repaired, or plan the methods or operations for shaping or assembling parts, based on blueprints, drawings, diagrams, or oral or written instructions. | Estimate the amounts, types, or costs of needed materials. | Install hardware, such as hinges, handles, catches, or drawer pulls, using hand tools. | Match materials for color, grain, or texture, giving attention to knots or other features of the wood. | Measure and mark dimensions of parts on paper or lumber stock prior to cutting, following blueprints, to ensure a tight fit and quality product. | Perform final touch-ups with sandpaper or steel wool. | Produce or assemble components of articles, such as store fixtures, office equipment, cabinets, or high-grade furniture. | Program computers to operate machinery. | Reinforce joints with nails or other fasteners to prepare articles for finishing. | Repair or alter wooden furniture, cabinetry, fixtures, paneling, or other pieces. | Set up or operate machines, including power saws, jointers, mortisers, tenoners, molders, or shapers, to cut, mold, or shape woodstock or wood substitutes. | Trim, sand, or scrape surfaces or joints to prepare articles for finishing. | Verify dimensions or check the quality or fit of pieces to ensure adherence to specifications.</t>
+  </si>
+  <si>
+    <t>51-7021.00</t>
+  </si>
+  <si>
+    <t>Furniture Finishers</t>
+  </si>
+  <si>
+    <t>Finish Repair Worker | Finisher | Furniture Finisher | Hand Sander | Lacquer Sprayer | Sander | Sealer Sander | Sprayer | Stain Sprayer | Stain Wiper</t>
+  </si>
+  <si>
+    <t>DuPont ColorNet | DuPont Spies Hecker Wizard | Intuit QuickBooks | Microsoft Office software | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Near Vision | Visual Color Discrimination | Arm-Hand Steadiness | Manual Dexterity | Control Precision | Visualization | Trunk Strength | Selective Attention | Static Strength | Dynamic Strength | Multilimb Coordination | Finger Dexterity | Flexibility of Closure | Category Flexibility | Inductive Reasoning | Problem Sensitivity | Oral Expression | Oral Comprehension | Deductive Reasoning | Written Comprehension | Perceptual Speed | Information Ordering | Speech Recognition | Far Vision</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Spend Time Standing | Importance of Being Exact or Accurate | Exposed to Hazardous Conditions | Face-to-Face Discussions with Individuals and Within Teams | Work Outcomes and Results of Other Workers | Time Pressure | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Making Repetitive Motions | Spend Time Walking or Running | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Cabinetmakers and Bench Carpenters | Carpet Installers | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Drywall and Ceiling Tile Installers | Fiberglass Laminators and Fabricators | Floor Layers, Except Carpet, Wood, and Hard Tiles | Floor Sanders and Finishers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Painters, Construction and Maintenance | Painting, Coating, and Decorating Workers | Shoe and Leather Workers and Repairers | Stone Cutters and Carvers, Manufacturing | Structural Metal Fabricators and Fitters | Terrazzo Workers and Finishers | Tile and Stone Setters | Upholsterers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Shape, finish, and refinish damaged, worn, or used furniture or new high-grade furniture to specified color or finish.</t>
+  </si>
+  <si>
+    <t>Brush bleaching agents on wood surfaces to restore natural color. | Brush, spray, or hand-rub finishing ingredients, such as paint, oil, stain, or wax, onto and into wood grain and apply lacquer or other sealers. | Confer with customers to determine furniture colors or finishes. | Design, create, and decorate entire pieces or specific parts of furniture, such as draws for cabinets. | Disassemble items to prepare them for finishing, using hand tools. | Distress surfaces with woodworking tools or abrasives before staining to create an antique appearance, or rub surfaces to bring out highlights and shadings. | Examine furniture to determine the extent of damage or deterioration, and to decide on the best method for repair or restoration. | Fill and smooth cracks or depressions, remove marks and imperfections, and repair broken parts, using plastic or wood putty, glue, nails, or screws. | Follow blueprints to produce specific designs. | Mix finish ingredients to obtain desired colors or shades. | Paint metal surfaces electrostatically, or by using a spray gun or other painting equipment. | Recommend woods, colors, finishes, and furniture styles, using knowledge of wood products, fashions, and styles. | Remove accessories prior to finishing, and mask areas that should not be exposed to finishing processes or substances. | Remove excess solvent, using cloths soaked in paint thinner. | Remove old finishes and damaged or deteriorated parts, using hand tools, stripping tools, sandpaper, steel wool, abrasives, solvents, or dip baths. | Replace or refurbish upholstery of items, using tacks, adhesives, softeners, solvents, stains, or polish. | Select appropriate finishing ingredients such as paint, stain, lacquer, shellac, or varnish, depending on factors such as wood hardness and surface type. | Smooth, shape, and touch up surfaces to prepare them for finishing, using sandpaper, pumice stones, steel wool, chisels, sanders, or grinders. | Spread graining ink over metal portions of furniture to simulate wood-grain finish. | Stencil, gild, emboss, mark, or paint designs or borders to reproduce the original appearance of restored pieces, or to decorate new pieces. | Treat warped or stained surfaces to restore original contours and colors. | Wash surfaces to prepare them for finish application.</t>
+  </si>
+  <si>
+    <t>51-7031.00</t>
+  </si>
+  <si>
+    <t>Model Makers, Wood</t>
+  </si>
+  <si>
+    <t>Builder | Craftsman | Jig Maker | Model Builder | Model Maker | Product Development Carpenter | Sample Builder | Sample Maker | Sample Worker | Wood Carver</t>
+  </si>
+  <si>
+    <t>Dassault Systemes CATIA | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Siemens NX</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Design | Building and Construction | Engineering and Technology | Mathematics | Administration and Management | Mechanical</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Finger Dexterity | Control Precision | Manual Dexterity | Visualization | Information Ordering | Problem Sensitivity | Oral Comprehension | Written Comprehension | Multilimb Coordination | Category Flexibility | Originality | Oral Expression | Perceptual Speed | Flexibility of Closure | Inductive Reasoning | Deductive Reasoning | Speech Clarity | Speech Recognition | Reaction Time | Selective Attention</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Equipment | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Spend Time Standing | Indoors, Not Environmentally Controlled | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Contact With Others | Determine Tasks, Priorities and Goals | Exposed to Contaminants | Work Outcomes and Results of Other Workers | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Cabinetmakers and Bench Carpenters | Carpenters | Engine and Other Machine Assemblers | Fabric and Apparel Patternmakers | Furniture Finishers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Layout Workers, Metal and Plastic | Machinists | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Model Makers, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Patternmakers, Metal and Plastic | Patternmakers, Wood | Sheet Metal Workers | Stone Cutters and Carvers, Manufacturing | Structural Metal Fabricators and Fitters | Tool and Die Makers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Construct full-size and scale wooden precision models of products. Includes wood jig builders and loft workers.</t>
+  </si>
+  <si>
+    <t>Build jigs that can be used as guides for assembling oversized or special types of box shooks. | Construct wooden models, patterns, templates, full scale mock-ups, and molds for parts of products and production tools. | Fabricate work aids such as scrapers or templates. | Finish patterns or models with protective or decorative coatings such as shellac, lacquer, or wax. | Fit, fasten, and assemble wood parts together to form patterns, models, or sections, using glue, nails, dowels, bolts, screws, and other fasteners. | Issue patterns to designated machine operators. | Maintain pattern records for reference. | Mark identifying information on patterns, parts, and templates to indicate assembly methods and details. | Plan, lay out, and draw outlines of units, sectional patterns, or full-scale mock-ups of products. | Read blueprints, drawings, or written specifications, and consult with designers to determine sizes and shapes of patterns and required machine setups. | Select wooden stock, determine layouts, and mark layouts of parts on stock, using precision equipment such as scribers, squares, and protractors. | Set up, operate, and adjust a variety of woodworking machines such as bandsaws and planers to cut and shape sections, parts, and patterns, according to specifications. | Trim, smooth, and shape surfaces, and plane, shave, file, scrape, and sand models to attain specified shapes, using hand tools. | Verify dimensions and contours of models during hand-forming processes, using templates and measuring devices.</t>
+  </si>
+  <si>
+    <t>51-7032.00</t>
+  </si>
+  <si>
+    <t>Patternmakers, Wood</t>
+  </si>
+  <si>
+    <t>Mold Maker | Pattern Engineer | Pattern Maker | Patternmaker | Wood Pattern Maker | Wood Patternmaker | Wood Shop Moldmaker | Woodshop Worker</t>
+  </si>
+  <si>
+    <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | Mastercam computer-aided design and manufacturing software | Microsoft Excel | Microsoft Office software | Microsoft Outlook</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Critical Thinking | Mathematics | Active Listening</t>
+  </si>
+  <si>
+    <t>Mathematics | Design | Engineering and Technology | Mechanical | Building and Construction | Administration and Management | Production and Processing | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Control Precision | Arm-Hand Steadiness | Near Vision | Reaction Time | Finger Dexterity | Information Ordering | Visualization | Static Strength | Multilimb Coordination | Selective Attention | Category Flexibility | Deductive Reasoning | Problem Sensitivity | Oral Comprehension | Perceptual Speed | Mathematical Reasoning | Oral Expression | Written Comprehension | Speech Clarity | Speech Recognition | Depth Perception | Trunk Strength</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Contact With Others | Exposed to Hazardous Equipment | Determine Tasks, Priorities and Goals | Time Pressure | Work With or Contribute to a Work Group or Team | Spend Time Standing | Frequency of Decision Making | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Repeating Same Tasks | E-Mail | Telephone Conversations | Physical Proximity | Work Outcomes and Results of Other Workers | Indoors, Not Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Cabinetmakers and Bench Carpenters | Carpenters | Etchers and Engravers | Fabric and Apparel Patternmakers | Foundry Mold and Coremakers | Grinding and Polishing Workers, Hand | Layout Workers, Metal and Plastic | Machinists | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Model Makers, Metal and Plastic | Model Makers, Wood | Molders, Shapers, and Casters, Except Metal and Plastic | Patternmakers, Metal and Plastic | Sheet Metal Workers | Stone Cutters and Carvers, Manufacturing | Structural Metal Fabricators and Fitters | Tool and Die Makers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Plan, lay out, and construct wooden unit or sectional patterns used in forming sand molds for castings.</t>
+  </si>
+  <si>
+    <t>Collect and store patterns and lumber. | Compute dimensions, areas, volumes, and weights. | Construct wooden models, templates, full scale mock-ups, jigs, or molds for shaping parts of products. | Correct patterns to compensate for defects in castings. | Divide patterns into sections according to shapes of castings to facilitate removal of patterns from molds. | Estimate costs for patternmaking jobs. | Finish completed products or models with shellac, lacquer, wax, or paint. | Fit, fasten, and assemble wood parts together to form patterns, models, or sections, using glue, nails, dowels, bolts, and screws. | Glue fillets along interior angles of patterns. | Inventory equipment and supplies, ordering parts and tools as necessary. | Issue patterns to designated machine operators. | Lay out patterns on wood stock and draw outlines of units, sectional patterns, or full-scale mock-ups of products, based on blueprint specifications and sketches, and using marking and measuring devices. | Maintain pattern records for reference. | Mark identifying information such as colors or codes on patterns, parts, and templates to indicate assembly methods. | Read blueprints, drawings, or written specifications to determine sizes and shapes of patterns and required machine setups. | Repair broken or damaged patterns. | Select lumber to be used for patterns. | Set up, operate, and adjust a variety of woodworking machines such as bandsaws and lathes to cut and shape sections, parts, and patterns, according to specifications. | Trim, smooth, and shape surfaces, and plane, shave, file, scrape, and sand models to attain specified shapes, using hand tools. | Verify dimensions of completed patterns, using templates, straightedges, calipers, or protractors.</t>
+  </si>
+  <si>
+    <t>51-7041.00</t>
+  </si>
+  <si>
+    <t>Sawing Machine Setters, Operators, and Tenders, Wood</t>
+  </si>
+  <si>
+    <t>Bandmill Operator | Cut Off Saw Operator | Edgerman | Knot Saw Operator | Panel Saw Operator | Planer | Resaw Operator | Rip Saw Operator | Saw Operator | Sawyer</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Automated inventory software | Computerized numerical control CNC software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Control Precision | Near Vision | Manual Dexterity | Arm-Hand Steadiness | Rate Control | Reaction Time | Problem Sensitivity | Finger Dexterity | Stamina | Trunk Strength | Multilimb Coordination | Selective Attention | Depth Perception | Far Vision | Static Strength | Inductive Reasoning | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Equipment | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Indoors, Not Environmentally Controlled | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Pace Determined by Speed of Equipment | Freedom to Make Decisions | Time Pressure | Determine Tasks, Priorities and Goals | Contact With Others | Spend Time Making Repetitive Motions | Spend Time Bending or Twisting Your Body | Work With or Contribute to a Work Group or Team | Exposed to Very Hot or Cold Temperatures | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sewing Machine Operators | Shoe Machine Operators and Tenders | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend wood sawing machines. May operate computer numerically controlled (CNC) equipment. Includes lead sawyers.</t>
+  </si>
+  <si>
+    <t>Adjust bolts, clamps, stops, guides, or table angles or heights, using hand tools. | Adjust saw blades, using wrenches and rulers, or by turning handwheels or pressing pedals, levers, or panel buttons. | Clear machine jams, using hand tools. | Count, sort, or stack finished workpieces. | Cut grooves, bevels, or miters, saw curved or irregular designs, and sever or shape metals, according to specifications or work orders. | Dispose of waste material after completing work assignments. | Examine blueprints, drawings, work orders, or patterns to determine equipment set-up or selection details, procedures to be used, or dimensions of final products. | Examine logs or lumber to plan the best cuts. | Guide workpieces against saws, saw over workpieces by hand, or operate automatic feeding devices to guide cuts. | Inspect and measure workpieces to mark for cuts and to verify the accuracy of cuts, using rulers, squares, or caliper rules. | Inspect stock for imperfections or to estimate grades or qualities of stock or workpieces. | Lubricate or clean machines, using wrenches, grease guns, or solvents. | Measure and mark stock for cuts. | Monitor sawing machines, adjusting speed and tension and clearing jams to ensure proper operation. | Mount and bolt sawing blades or attachments to machine shafts. | Operate panelboards of saw or conveyor systems to move stock through processes or to cut stock to specified dimensions. | Position and clamp stock on tables, conveyors, or carriages, using hoists, guides, stops, dogs, wedges, or wrenches. | Select saw blades, types or grades of stock, or cutting procedures to be used, according to work orders or supervisors' instructions. | Set up, operate, or tend saws or machines that cut or trim wood to specified dimensions, such as circular saws, band saws, multiple-blade sawing machines, scroll saws, ripsaws, or crozer machines. | Sharpen blades, or replace defective or worn blades or bands, using hand tools. | Trim lumber to straighten rough edges or remove defects, using circular saws. | Unclamp and remove finished workpieces from tables.</t>
+  </si>
+  <si>
+    <t>51-7042.00</t>
+  </si>
+  <si>
+    <t>Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Boring Machine Operator | Cabinet Maker | Knot Saw Operator | Lathe Operator | Machine Operator | Molder Operator | Router Operator | Sander | Sander Operator</t>
+  </si>
+  <si>
+    <t>AS/400 Database | Adobe Acrobat | Adobe Creative Cloud software | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apple macOS | Autodesk AutoCAD | Computer aided design and drafting CADD software | Computerized numerical control CNC software | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Inventory control software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Oracle Java | Timekeeping software | Vero Software ALPHACAM | YouTube</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Near Vision | Reaction Time | Control Precision | Manual Dexterity | Oral Comprehension | Problem Sensitivity | Multilimb Coordination | Static Strength | Trunk Strength | Auditory Attention | Far Vision | Finger Dexterity | Arm-Hand Steadiness | Selective Attention | Visualization | Perceptual Speed | Oral Expression | Category Flexibility | Information Ordering | Deductive Reasoning | Speech Recognition | Extent Flexibility | Dynamic Strength | Rate Control | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>Exposed to Contaminants | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | Indoors, Not Environmentally Controlled | Exposed to Hazardous Equipment | Importance of Being Exact or Accurate | Spend Time Making Repetitive Motions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Time Pressure | Spend Time Bending or Twisting Your Body | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Repeating Same Tasks | Contact With Others | Frequency of Decision Making | Exposed to Very Hot or Cold Temperatures</t>
+  </si>
+  <si>
+    <t>Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sawing Machine Setters, Operators, and Tenders, Wood | Shoe Machine Operators and Tenders | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend woodworking machines, such as drill presses, lathes, shapers, routers, sanders, planers, and wood nailing machines. May operate computer numerically controlled (CNC) equipment.</t>
+  </si>
+  <si>
+    <t>Adjust machine tables or cutting devices and set controls on machines to produce specified cuts or operations. | Attach and adjust guides, stops, clamps, chucks, or feed mechanisms, using hand tools. | Change alignment and adjustment of sanding, cutting, or boring machine guides to prevent defects in finished products, using hand tools. | Clean or maintain products, machines, or work areas. | Control hoists to remove parts or products from work stations. | Determine product specifications and materials, work methods, and machine setup requirements, according to blueprints, oral or written instructions, drawings, or work orders. | Examine finished workpieces for smoothness, shape, angle, depth-of-cut, or conformity to specifications and verify dimensions, visually and using hands, rules, calipers, templates, or gauges. | Examine raw woodstock for defects and to ensure conformity to size and other specification standards. | Feed stock through feed mechanisms or conveyors into planing, shaping, boring, mortising, or sanding machines to produce desired components. | Grease or oil woodworking machines. | Inspect and mark completed workpieces and stack them on pallets, in boxes, or on conveyors so that they can be moved to the next workstation. | Inspect pulleys, drive belts, guards, or fences on machines to ensure that machines will operate safely. | Install and adjust blades, cutterheads, boring-bits, or sanding-belts, using hand tools and rules. | Monitor operation of machines and make adjustments to correct problems and ensure conformance to specifications. | Operate gluing machines to glue pieces of wood together, or to press and affix wood veneer to wood surfaces. | Push or hold workpieces against, under, or through cutting, boring, or shaping mechanisms. | Remove and replace worn parts, bits, belts, sandpaper, or shaping tools. | Secure woodstock against a guide or in a holding device, place woodstock on a conveyor, or dump woodstock in a hopper to feed woodstock into machines. | Select knives, saws, blades, cutter heads, cams, bits, or belts, according to workpiece, machine functions, or product specifications. | Set up, program, operate, or tend computerized or manual woodworking machines, such as drill presses, lathes, shapers, routers, sanders, planers, or wood-nailing machines. | Set up, program, or control computer-aided design (CAD) or computer numerical control (CNC) machines. | Start machines and move levers to engage hydraulic lifts that press woodstocks into desired forms and disengage lifts after appropriate drying times. | Start machines, adjust controls, and make trial cuts to ensure that machinery is operating properly. | Trim wood parts according to specifications, using planes, chisels, or wood files or sanders. | Unclamp workpieces and remove them from machines.</t>
+  </si>
+  <si>
+    <t>51-7099.00</t>
+  </si>
+  <si>
+    <t>Woodworkers, All Other</t>
+  </si>
+  <si>
+    <t>Millwork Worker | Wood Assembler | Wood Finisher | Wood Machine Operator | Wood Products Worker | Woodshop Worker | Woodworker | Lumber Worker | Wood Fabricator | Joinery Worker</t>
+  </si>
+  <si>
+    <t>Supervisory control and data acquisition SCADA software | Programmable logic controller PLC software | Statistical process control SPC software | Materials requirement planning MRP software | Computerized maintenance management system CMMS | Microsoft Excel | Microsoft Word | Email software | Inventory management systems | Enterprise resource planning ERP system | Database software | SAP software | Autodesk AutoCAD</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Design | Mathematics | English Language | Building and Construction | Chemistry</t>
+  </si>
+  <si>
+    <t>Cabinetmakers and Bench Carpenters | Furniture Finishers | Model Makers, Wood | Patternmakers, Wood | Sawing Machine Setters, Operators, and Tenders, Wood | Woodworking Machine Setters, Operators, and Tenders, Except Sawing | Carpenters | Helpers--Carpenters | Upholsterers | Floor Sanders and Finishers | Painting, Coating, and Decorating Workers | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Inspectors, Testers, Sorters, Samplers, and Weighers | Computer Numerically Controlled Tool Operators | First-Line Supervisors of Production and Operating Workers | Helpers--Production Workers | Production Workers, All Other | Log Graders and Scalers | Adhesive Bonding Machine Operators and Tenders | Molders, Shapers, and Casters, Except Metal and Plastic</t>
+  </si>
+  <si>
+    <t>All woodworkers not listed separately.</t>
+  </si>
+  <si>
+    <t>Fabricate wood products in specialties not classified separately. | Read blueprints, drawings, and cutting lists to determine work requirements. | Measure, mark, and lay out wood stock for cutting and shaping. | Operate saws, planers, routers, sanders, and shaping machines. | Assemble wood components using glue, fasteners, dowels, and joinery. | Sand, stain, seal, and finish wood surfaces. | Inspect materials for defects, moisture content, and grain quality. | Verify dimensions and squareness of assembled products. | Set up and adjust machine guides, blades, and cutting heads. | Perform routine maintenance and sharpening of tools and blades. | Record production data, material usage, and scrap. | Follow safety procedures for saws, dust collection, and finishing chemicals. | Package and prepare finished wood products for shipment or installation. | Repair damaged or defective wood pieces to restore quality.</t>
+  </si>
+  <si>
+    <t>51-8011.00</t>
+  </si>
+  <si>
+    <t>Nuclear Power Reactor Operators</t>
+  </si>
+  <si>
+    <t>Licensed Reactor Operator | Nuclear Control Operator | Nuclear Control Room Operator | Nuclear Plant Operator (NPO) | Nuclear Power Reactor Operator | Nuclear Reactor Operator | Nuclear Station Operator (NSO) | Nuclear Supervising Operator (NSO) | Nuclear Unit Operator | Reactor Operator (RO)</t>
+  </si>
+  <si>
+    <t>Data logging software | Microsoft Access | Microsoft Azure software | Microsoft Excel | Microsoft Office software | Microsoft Power Automate | Microsoft Power BI | Microsoft PowerPoint | Microsoft SharePoint | Outage management system OMS | Plant information data entry software | Structured query language SQL</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Active Listening | Critical Thinking | Writing | Speaking | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Physics | Mechanical | Public Safety and Security | Mathematics | Engineering and Technology | Chemistry | Design</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Written Comprehension | Oral Expression | Information Ordering | Perceptual Speed | Near Vision | Deductive Reasoning | Inductive Reasoning | Written Expression | Speech Clarity | Selective Attention | Flexibility of Closure | Speech Recognition | Far Vision | Category Flexibility | Mathematical Reasoning | Originality | Fluency of Ideas | Time Sharing | Auditory Attention | Hearing Sensitivity | Visual Color Discrimination</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Telephone Conversations | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | E-Mail | Contact With Others | Consequence of Error | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Frequency of Decision Making | Importance of Repeating Same Tasks | Work Outcomes and Results of Other Workers | Physical Proximity | Exposed to Radiation | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Biomass Plant Technicians | Biomass Power Plant Managers | Chemical Engineers | Chemical Plant and System Operators | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Gas Plant Operators | Geothermal Production Managers | Geothermal Technicians | Hydroelectric Plant Technicians | Hydroelectric Production Managers | Nuclear Engineers | Nuclear Monitoring Technicians | Nuclear Technicians | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Distributors and Dispatchers | Power Plant Operators | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Operate or control nuclear reactors. Move control rods, start and stop equipment, monitor and adjust controls, and record data in logs. Implement emergency procedures when needed. May respond to abnormalities, determine cause, and recommend corrective action.</t>
+  </si>
+  <si>
+    <t>Adjust controls to position rod and to regulate flux level, reactor period, coolant temperature, or rate of power flow, following standard procedures. | Authorize actions to correct identified operational inefficiencies or hazards so that operating efficiency is maximized and potential environmental issues are minimized. | Authorize maintenance activities on units or changes in equipment or system operational status. | Conduct inspections or operations outside of control rooms as necessary. | Develop or implement actions such as lockouts, tagouts, or clearances to allow equipment to be safely repaired. | Direct measurement of the intensity or types of radiation in work areas, equipment, or materials. | Direct reactor operators in emergency situations, in accordance with emergency operating procedures. | Direct the collection and testing of air, water, gas, or solid samples to determine radioactivity levels or to ensure appropriate radioactive containment. | Dispatch orders or instructions to personnel through radiotelephone or intercommunication systems to coordinate auxiliary equipment operation. | Implement operational procedures, such as those controlling start-up or shut-down activities. | Monitor all systems for normal running conditions, performing activities such as checking gauges to assess output or the effects of generator loading on other equipment. | Monitor or operate boilers, turbines, wells, or auxiliary power plant equipment. | Note malfunctions of equipment, instruments, or controls and report these conditions to supervisors. | Operate nuclear power reactors in accordance with policies and procedures to protect workers from radiation and to ensure environmental safety. | Participate in nuclear fuel element handling activities, such as preparation, transfer, loading, or unloading. | Record operating data, such as the results of surveillance tests. | Respond to system or unit abnormalities, diagnosing the cause, and recommending or taking corrective action. | Review and edit standard operating procedures. | Supervise technicians' work activities to ensure that equipment is operated in accordance with policies and procedures that protect workers from radiation and ensure environmental safety.</t>
+  </si>
+  <si>
+    <t>51-8012.00</t>
+  </si>
+  <si>
+    <t>Power Distributors and Dispatchers</t>
+  </si>
+  <si>
+    <t>Control Area Operator | Control Operator | DSO (Distribution System Operator) | Dispatcher | Distribution System Dispatcher (DSD) | Electric System Operator | Power System Dispatcher | Power System Operator | Systems Operator | Transmission System Operator (TSO)</t>
+  </si>
+  <si>
+    <t>ABB MicroSCADA Pro DMS | ABB MicroSCADA Pro SYS | ABB PSGuard | Catapult Software iPower SCADA | Distribution automation system software | Distribution management system DMS | Energy management system EMS | Geographic information system GIS software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Milsoft DisSPatch | OSI monarch/SGP | Outage management system OMS | Radius NetMan | Radius Uni-View | SAP software | Siemens Energy and Automation | Siemens Spectrum Power TG | Siemens Spectrum PowerCC Distribution Management | Substation automation system software | Substation monitoring system software | Supervisory control and data acquisition SCADA software | Telvent Responder Outage Management System OMS | Wide area monitoring system WAMS software | Wide area remote control system software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Critical Thinking | Monitoring | Speaking | Writing | Active Learning</t>
+  </si>
+  <si>
+    <t>English Language | Public Safety and Security | Mathematics | Computers and Electronics | Telecommunications | Engineering and Technology | Customer and Personal Service | Mechanical | Education and Training | Physics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Inductive Reasoning | Oral Comprehension | Oral Expression | Written Comprehension | Deductive Reasoning | Near Vision | Written Expression | Information Ordering | Speech Clarity | Perceptual Speed | Speech Recognition | Far Vision | Selective Attention | Visualization | Flexibility of Closure | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Consequence of Error | Impact of Decisions on Co-workers or Company Results | Contact With Others | Importance of Being Exact or Accurate | E-Mail | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Importance of Repeating Same Tasks | Freedom to Make Decisions | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Physical Proximity | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Deal With External Customers or the Public in General | Level of Competition</t>
+  </si>
+  <si>
+    <t>Biomass Plant Technicians | Biomass Power Plant Managers | Broadcast Technicians | Control and Valve Installers and Repairers, Except Mechanical Door | Electrical Engineers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electronics Engineers, Except Computer | Gas Plant Operators | Geothermal Technicians | Hydroelectric Plant Technicians | Lighting Technicians | Mechanical Engineers | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Plant Operators | Stationary Engineers and Boiler Operators | Telecommunications Equipment Installers and Repairers, Except Line Installers | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Coordinate, regulate, or distribute electricity or steam.</t>
+  </si>
+  <si>
+    <t>Calculate load estimates or equipment requirements to determine required control settings. | Control, monitor, or operate equipment that regulates or distributes electricity or steam, using data obtained from instruments or computers. | Coordinate with engineers, planners, field personnel, or other utility workers to provide information such as clearances, switching orders, or distribution process changes. | Direct personnel engaged in controlling or operating distribution equipment or machinery, such as instructing control room operators to start boilers or generators. | Distribute or regulate the flow of power between entities, such as generating stations, substations, distribution lines, or users, keeping track of the status of circuits or connections. | Implement energy schedules, including real-time transmission reservations or schedules. | Inspect equipment to ensure that specifications are met or to detect any defects. | Manipulate controls to adjust or activate power distribution equipment or machines. | Monitor and record switchboard or control board readings to ensure that electrical or steam distribution equipment is operating properly. | Prepare switching orders that will isolate work areas without causing power outages, referring to drawings of power systems. | Record and compile operational data, such as chart or meter readings, power demands, or usage and operating times, using transmission system maps. | Respond to emergencies, such as transformer or transmission line failures, and route current around affected areas. | Tend auxiliary equipment used in the power distribution process. | Track conditions that could affect power needs, such as changes in the weather, and adjust equipment to meet any anticipated changes.</t>
+  </si>
+  <si>
+    <t>51-8013.00</t>
+  </si>
+  <si>
+    <t>Power Plant Operators</t>
+  </si>
+  <si>
+    <t>Auxiliary Operator | Control Operator | Control Room Operator | Multicraft Operator (MCO) | Operations and Maintenance Technician (O and M Tech) | Plant Control Operator | Plant Operator | Power Plant Operator | Station Operator | Unit Operator</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | Continuous emissions monitoring systems CEMS | Distributed control system DCS | Email software | Emerson Ovation | Gas field monitoring system software | General Electric Mark VI Distributed Control System DCS | General Electric Mark VI Integrated Control System ICS | Interlock shutdown systems | Landfill gas analysis software | Landtec System Software LFG Pro | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Operational Data Store ODS software | SAP software | Safety instrumented system SIS software | Siemens Power Plant Automation SPPA | Siemens Teleperm | Supervisory control and data acquisition SCADA software | Teknik Segala OSI Plant Information PI System | Web browser software | Yokogawa FAST/TOOLS</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Monitoring | Active Listening | Reading Comprehension | Writing</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | English Language | Production and Processing | Chemistry | Physics | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Deductive Reasoning | Near Vision | Oral Expression | Inductive Reasoning | Information Ordering | Perceptual Speed | Far Vision | Manual Dexterity | Selective Attention | Flexibility of Closure | Written Comprehension | Written Expression | Category Flexibility | Speech Clarity | Speech Recognition | Auditory Attention | Reaction Time | Control Precision | Finger Dexterity | Arm-Hand Steadiness | Time Sharing</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Hazardous Conditions | Work With or Contribute to a Work Group or Team | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Consequence of Error | Telephone Conversations | Exposed to Very Hot or Cold Temperatures | Exposed to High Places | Impact of Decisions on Co-workers or Company Results | Exposed to Contaminants | Health and Safety of Other Workers | Freedom to Make Decisions | Outdoors, Exposed to All Weather Conditions | Importance of Being Exact or Accurate | Exposed to Hazardous Equipment | Indoors, Not Environmentally Controlled | Exposed to Extremely Bright or Inadequate Lighting Conditions | Indoors, Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Physical Proximity | Outdoors, Under Cover | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | In an Enclosed Vehicle or Operate Enclosed Equipment | Time Pressure | Exposed to Minor Burns, Cuts, Bites, or Stings | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Biofuels Processing Technicians | Biomass Plant Technicians | Biomass Power Plant Managers | Chemical Plant and System Operators | Control and Valve Installers and Repairers, Except Mechanical Door | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Geothermal Production Managers | Geothermal Technicians | Hydroelectric Plant Technicians | Hydroelectric Production Managers | Nuclear Power Reactor Operators | Nuclear Technicians | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Distributors and Dispatchers | Pump Operators, Except Wellhead Pumpers | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators | Wellhead Pumpers | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Control, operate, or maintain machinery to generate electric power. Includes auxiliary equipment operators.</t>
+  </si>
+  <si>
+    <t>Adjust controls to generate specified electrical power or to regulate the flow of power between generating stations and substations. | Analyze the layout, instrumentation, or function of electrical generation or transmission facilities. | Clean, lubricate, or maintain equipment, such as generators, turbines, pumps, or compressors, to prevent failure or deterioration. | Collect oil, water, or electrolyte samples for laboratory analysis. | Communicate with systems operators to regulate and coordinate line voltages and transmission loads and frequencies. | Control generator output to match the phase, frequency, or voltage of electricity supplied to panels. | Control or maintain auxiliary equipment, such as pumps, fans, compressors, condensers, feedwater heaters, filters, or chlorinators, to supply water, fuel, lubricants, air, or auxiliary power. | Control power generating equipment, including boilers, turbines, generators, or reactors, using control boards or semi-automatic equipment. | Diagnose or troubleshoot problems with gas collection systems. | Examine and test electrical power distribution machinery and equipment, using testing devices. | Inspect records or log book entries or communicate with plant personnel to assess equipment operating status. | Make adjustments or minor repairs, such as tightening leaking gland or pipe joints. | Monitor power plant equipment and indicators to detect evidence of operating problems. | Monitor well fields periodically to ensure proper functioning and performance. | Open and close valves and switches in sequence to start or shut down auxiliary units. | Operate landfill gas, methane, or natural gas fueled electrical generation systems. | Operate or maintain distributed power generation equipment, including fuel cells or microturbines, to produce energy on-site for manufacturing or other commercial purposes. | Operate, control, or monitor equipment, such as acid or gas carbon dioxide removal units, carbon dioxide compressors, or pipelines, to capture, store, or transport carbon dioxide exhaust. | Operate, control, or monitor gasifiers or related equipment, such as coolers, water quenches, water gas shifts reactors, or sulfur recovery units, to produce syngas or electricity from coal. | Operate, control, or monitor integrated gasification combined cycle (IGCC) or related equipment, such as air separation units, to generate electricity from coal. | Place standby emergency electrical generators on line in emergencies and monitor the temperature, output, and lubrication of the system. | Prepare and submit compliance, operational, and safety forms or reports. | Receive outage calls and request necessary personnel during power outages or emergencies. | Record and compile operational data by completing and maintaining forms, logs, or reports. | Regulate equipment operations and conditions, such as water levels, based on instrument data or from computers. | Repair or replace gas piping. | Start or stop generators, auxiliary pumping equipment, turbines, or other power plant equipment as necessary. | Take regulatory action, based on readings from charts, meters and gauges, at established intervals. | Trace electrical circuitry to ensure compliance of electrical systems with applicable codes or laws. | Verify that well field monitoring data conforms to applicable regulations.</t>
+  </si>
+  <si>
+    <t>51-8013.03</t>
+  </si>
+  <si>
+    <t>Biomass Plant Technicians</t>
+  </si>
+  <si>
+    <t>Auxiliary Operator | Central Heating Plant Operator | Fuel Handler | Fuel Quality Technician (Fuel Quality Tech) | Heating Plant Operator | Operations Technician (Operations Tech) | Plant Operator | Plant Technician | Steam Plant Operator</t>
+  </si>
+  <si>
+    <t>Distributed control system DCS | Energy analysis software | Inventory control software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | National Instruments LabVIEW</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Learning Strategies | Active Learning | Speaking | Writing | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Chemistry | English Language | Production and Processing | Engineering and Technology | Education and Training | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Near Vision | Control Precision | Problem Sensitivity | Information Ordering | Written Comprehension | Deductive Reasoning | Perceptual Speed | Multilimb Coordination | Reaction Time | Visual Color Discrimination | Far Vision | Rate Control | Arm-Hand Steadiness | Selective Attention | Visualization | Inductive Reasoning | Auditory Attention | Hearing Sensitivity | Manual Dexterity | Time Sharing | Written Expression | Oral Expression | Oral Comprehension | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Frequency of Decision Making | Exposed to Hazardous Conditions | Exposed to Contaminants | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Exposed to High Places | Importance of Repeating Same Tasks | Exposed to Very Hot or Cold Temperatures | Consequence of Error | Contact With Others | Exposed to Minor Burns, Cuts, Bites, or Stings | Work Outcomes and Results of Other Workers | Indoors, Environmentally Controlled | Exposed to Hazardous Equipment | Telephone Conversations | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Exposed to Extremely Bright or Inadequate Lighting Conditions | Importance of Being Exact or Accurate | Coordinate or Lead Others in Accomplishing Work Activities | Indoors, Not Environmentally Controlled | Outdoors, Exposed to All Weather Conditions | Pace Determined by Speed of Equipment | Written Letters and Memos | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Biofuels Processing Technicians | Biofuels Production Managers | Biofuels/Biodiesel Technology and Product Development Managers | Biomass Power Plant Managers | Chemical Engineers | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Geothermal Production Managers | Geothermal Technicians | Hydroelectric Plant Technicians | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators | Wellhead Pumpers | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Control and monitor biomass plant activities and perform maintenance as needed.</t>
+  </si>
+  <si>
+    <t>Assess quality of biomass feedstock. | Calculate, measure, load, or mix biomass feedstock for power generation. | Calibrate liquid flow devices or meters, including fuel, chemical, and water meters. | Clean work areas to ensure compliance with safety regulations. | Inspect biomass power plant or processing equipment, recording or reporting damage and mechanical problems. | Manage parts and supply inventories for biomass plants. | Measure and monitor raw biomass feedstock, including wood, waste, or refuse materials. | Operate biomass fuel-burning boiler or biomass fuel gasification system equipment in accordance with specifications or instructions. | Operate equipment to heat biomass, using knowledge of controls, combustion, and firing mechanisms. | Operate equipment to start, stop, or regulate biomass-fueled generators, generator units, boilers, engines, or auxiliary systems. | Operate heavy equipment, such as bulldozers and front-end loaders. | Operate high-pressure steam boiler or water chiller equipment for electrical cogeneration operations. | Operate valves, pumps, engines, or generators to control and adjust production of biofuels or biomass-fueled power. | Perform routine maintenance or make minor repairs to mechanical, electrical, or electronic equipment in biomass plants. | Perform tests of water chemistry in boilers. | Preprocess feedstock to prepare for biochemical or thermochemical production processes. | Read and interpret instruction manuals or technical drawings related to biomass-fueled power or biofuels production equipment or processes. | Record or report operational data, such as readings on meters, instruments, and gauges.</t>
+  </si>
+  <si>
+    <t>51-8013.04</t>
+  </si>
+  <si>
+    <t>Hydroelectric Plant Technicians</t>
+  </si>
+  <si>
+    <t>Hydro Plant Technician (Hydro Plant Tech) | Hydro Technician (Hydro Tech) | Hydroelectric Mechanic | Hydroelectric Operations and Maintenance Technician (Hydro O and M Technician) | Hydroelectric Operator | Hydroelectric Plant Mechanic | Operations and Maintenance Technician (O and M Technician) | Plant Mechanic | Power Plant Mechanic | Power Plant Technician (Power Plant Tech)</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | Distributed control system DCS | IBM Lotus Notes | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Supervisory control and data acquisition SCADA software | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Reading Comprehension | Active Listening | Speaking | Active Learning | Mathematics | Writing</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | Mathematics | Engineering and Technology | Education and Training | Design | English Language | Computers and Electronics | Physics | Building and Construction | Administration and Management | Production and Processing | Law and Government | Transportation | Telecommunications | Administrative | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Information Ordering | Control Precision | Oral Comprehension | Deductive Reasoning | Inductive Reasoning | Selective Attention | Oral Expression | Speech Recognition | Visualization | Perceptual Speed | Written Comprehension | Far Vision | Speech Clarity | Extent Flexibility | Multilimb Coordination | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Flexibility of Closure | Written Expression | Category Flexibility | Visual Color Discrimination | Gross Body Equilibrium | Trunk Strength</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Work With or Contribute to a Work Group or Team | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Telephone Conversations | Indoors, Not Environmentally Controlled | In an Enclosed Vehicle or Operate Enclosed Equipment | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Exposed to Very Hot or Cold Temperatures | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Outdoors, Exposed to All Weather Conditions | Frequency of Decision Making | Work Outcomes and Results of Other Workers | Indoors, Environmentally Controlled | Exposed to Extremely Bright or Inadequate Lighting Conditions | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Biomass Plant Technicians | Biomass Power Plant Managers | Control and Valve Installers and Repairers, Except Mechanical Door | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Gas Plant Operators | Geothermal Production Managers | Geothermal Technicians | Hydroelectric Production Managers | Maintenance and Repair Workers, General | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Distributors and Dispatchers | Power Plant Operators | Ship Engineers | Solar Photovoltaic Installers | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators | Wellhead Pumpers | Wind Energy Engineers | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Monitor and control activities associated with hydropower generation. Operate plant equipment, such as turbines, pumps, valves, gates, fans, electric control boards, and battery banks. Monitor equipment operation and performance and make necessary adjustments to ensure optimal performance. Perform equipment maintenance and repair as necessary.</t>
+  </si>
+  <si>
+    <t>Change oil, hydraulic fluid, or other lubricants to maintain condition of hydroelectric plant equipment. | Communicate status of hydroelectric operating equipment to dispatchers or supervisors. | Connect metal parts or components in hydroelectric plants by welding, soldering, riveting, tapping, bolting, bonding, or screwing. | Cut, bend, or shape metal for applications in hydroelectric plants, using equipment such as hydraulic benders or pipe threaders. | Erect scaffolds, platforms, or hoisting frames to access hydroelectric plant machinery or infrastructure for repair or replacement. | Identify or address malfunctions of hydroelectric plant operational equipment, such as generators, transformers, or turbines. | Implement load or switching orders in hydroelectric plants, in accordance with specifications or instructions. | Inspect water-powered electric generators or auxiliary equipment in hydroelectric plants to verify proper operation or to determine maintenance or repair needs. | Install or calibrate electrical or mechanical equipment, such as motors, engines, switchboards, relays, switch gears, meters, pumps, hydraulics, or flood channels. | Lift and move loads, using cranes, hoists, and rigging, to install or repair hydroelectric system equipment or infrastructure. | Maintain logs, reports, work requests, or other records of work performed in hydroelectric plants. | Maintain or repair hydroelectric plant electrical, mechanical, or electronic equipment, such as motors, transformers, voltage regulators, generators, relays, battery systems, air compressors, sump pumps, gates, or valves. | Monitor hydroelectric power plant equipment operation and performance, adjusting to performance specifications, as necessary. | Operate high voltage switches or related devices in hydropower stations. | Operate hydroelectric plant equipment, such as turbines, pumps, valves, gates, fans, electric control boards, or battery banks. | Perform preventive or corrective containment or cleanup measures in hydroelectric plants to prevent environmental contamination. | Perform tunnel or field inspections of hydroelectric plant facilities or resources. | Splice or terminate cables or electrical wiring in hydroelectric plants. | Start, adjust, or stop generating units, operating valves, gates, or auxiliary equipment in hydroelectric power generating plants. | Take readings and record data, such as water levels, temperatures, or flow rates. | Test and repair or replace electrical equipment, such as circuit breakers, station batteries, cable trays, conduits, or control devices.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1928,1761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" t="s">
+        <v>106</v>
+      </c>
+      <c r="J10" t="s">
+        <v>107</v>
+      </c>
+      <c r="K10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" t="s">
+        <v>117</v>
+      </c>
+      <c r="J11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" t="s">
+        <v>137</v>
+      </c>
+      <c r="H13" t="s">
+        <v>138</v>
+      </c>
+      <c r="I13" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14" t="s">
+        <v>148</v>
+      </c>
+      <c r="I14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J14" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" t="s">
+        <v>157</v>
+      </c>
+      <c r="G15" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J15" t="s">
+        <v>161</v>
+      </c>
+      <c r="K15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" t="s">
+        <v>167</v>
+      </c>
+      <c r="F16" t="s">
+        <v>168</v>
+      </c>
+      <c r="G16" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" t="s">
+        <v>171</v>
+      </c>
+      <c r="J16" t="s">
+        <v>172</v>
+      </c>
+      <c r="K16" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" t="s">
+        <v>178</v>
+      </c>
+      <c r="F17" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" t="s">
+        <v>180</v>
+      </c>
+      <c r="H17" t="s">
+        <v>181</v>
+      </c>
+      <c r="I17" t="s">
+        <v>182</v>
+      </c>
+      <c r="J17" t="s">
+        <v>183</v>
+      </c>
+      <c r="K17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" t="s">
+        <v>190</v>
+      </c>
+      <c r="G18" t="s">
+        <v>191</v>
+      </c>
+      <c r="H18" t="s">
+        <v>192</v>
+      </c>
+      <c r="I18" t="s">
+        <v>193</v>
+      </c>
+      <c r="J18" t="s">
+        <v>194</v>
+      </c>
+      <c r="K18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C19" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19" t="s">
+        <v>199</v>
+      </c>
+      <c r="E19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" t="s">
+        <v>200</v>
+      </c>
+      <c r="G19" t="s">
+        <v>201</v>
+      </c>
+      <c r="H19" t="s">
+        <v>202</v>
+      </c>
+      <c r="I19" t="s">
+        <v>203</v>
+      </c>
+      <c r="J19" t="s">
+        <v>204</v>
+      </c>
+      <c r="K19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" t="s">
+        <v>209</v>
+      </c>
+      <c r="E20" t="s">
+        <v>210</v>
+      </c>
+      <c r="F20" t="s">
+        <v>211</v>
+      </c>
+      <c r="G20" t="s">
+        <v>212</v>
+      </c>
+      <c r="H20" t="s">
+        <v>213</v>
+      </c>
+      <c r="I20" t="s">
+        <v>214</v>
+      </c>
+      <c r="J20" t="s">
+        <v>215</v>
+      </c>
+      <c r="K20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" t="s">
+        <v>223</v>
+      </c>
+      <c r="H21" t="s">
+        <v>224</v>
+      </c>
+      <c r="I21" t="s">
+        <v>225</v>
+      </c>
+      <c r="J21" t="s">
+        <v>226</v>
+      </c>
+      <c r="K21" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" t="s">
+        <v>230</v>
+      </c>
+      <c r="D22" t="s">
+        <v>231</v>
+      </c>
+      <c r="E22" t="s">
+        <v>232</v>
+      </c>
+      <c r="F22" t="s">
+        <v>233</v>
+      </c>
+      <c r="G22" t="s">
+        <v>234</v>
+      </c>
+      <c r="H22" t="s">
+        <v>235</v>
+      </c>
+      <c r="I22" t="s">
+        <v>236</v>
+      </c>
+      <c r="J22" t="s">
+        <v>237</v>
+      </c>
+      <c r="K22" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>239</v>
+      </c>
+      <c r="B23" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" t="s">
+        <v>243</v>
+      </c>
+      <c r="F23" t="s">
+        <v>244</v>
+      </c>
+      <c r="G23" t="s">
+        <v>245</v>
+      </c>
+      <c r="H23" t="s">
+        <v>246</v>
+      </c>
+      <c r="I23" t="s">
+        <v>247</v>
+      </c>
+      <c r="J23" t="s">
+        <v>248</v>
+      </c>
+      <c r="K23" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>250</v>
+      </c>
+      <c r="B24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" t="s">
+        <v>252</v>
+      </c>
+      <c r="D24" t="s">
+        <v>253</v>
+      </c>
+      <c r="E24" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" t="s">
+        <v>255</v>
+      </c>
+      <c r="G24" t="s">
+        <v>256</v>
+      </c>
+      <c r="H24" t="s">
+        <v>257</v>
+      </c>
+      <c r="I24" t="s">
+        <v>258</v>
+      </c>
+      <c r="J24" t="s">
+        <v>259</v>
+      </c>
+      <c r="K24" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>261</v>
+      </c>
+      <c r="B25" t="s">
+        <v>262</v>
+      </c>
+      <c r="C25" t="s">
+        <v>263</v>
+      </c>
+      <c r="D25" t="s">
+        <v>264</v>
+      </c>
+      <c r="E25" t="s">
+        <v>265</v>
+      </c>
+      <c r="F25" t="s">
+        <v>255</v>
+      </c>
+      <c r="G25" t="s">
+        <v>266</v>
+      </c>
+      <c r="H25" t="s">
+        <v>267</v>
+      </c>
+      <c r="I25" t="s">
+        <v>268</v>
+      </c>
+      <c r="J25" t="s">
+        <v>269</v>
+      </c>
+      <c r="K25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" t="s">
+        <v>273</v>
+      </c>
+      <c r="D26" t="s">
+        <v>274</v>
+      </c>
+      <c r="E26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" t="s">
+        <v>275</v>
+      </c>
+      <c r="G26" t="s">
+        <v>276</v>
+      </c>
+      <c r="H26" t="s">
+        <v>277</v>
+      </c>
+      <c r="I26" t="s">
+        <v>278</v>
+      </c>
+      <c r="J26" t="s">
+        <v>279</v>
+      </c>
+      <c r="K26" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>281</v>
+      </c>
+      <c r="B27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C27" t="s">
+        <v>283</v>
+      </c>
+      <c r="D27" t="s">
+        <v>284</v>
+      </c>
+      <c r="E27" t="s">
+        <v>285</v>
+      </c>
+      <c r="F27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" t="s">
+        <v>286</v>
+      </c>
+      <c r="H27" t="s">
+        <v>287</v>
+      </c>
+      <c r="I27" t="s">
+        <v>288</v>
+      </c>
+      <c r="J27" t="s">
+        <v>289</v>
+      </c>
+      <c r="K27" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>291</v>
+      </c>
+      <c r="B28" t="s">
+        <v>292</v>
+      </c>
+      <c r="C28" t="s">
+        <v>293</v>
+      </c>
+      <c r="D28" t="s">
+        <v>294</v>
+      </c>
+      <c r="E28" t="s">
+        <v>295</v>
+      </c>
+      <c r="F28" t="s">
+        <v>296</v>
+      </c>
+      <c r="G28" t="s">
+        <v>297</v>
+      </c>
+      <c r="H28" t="s">
+        <v>298</v>
+      </c>
+      <c r="I28" t="s">
+        <v>299</v>
+      </c>
+      <c r="J28" t="s">
+        <v>300</v>
+      </c>
+      <c r="K28" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>302</v>
+      </c>
+      <c r="B29" t="s">
+        <v>303</v>
+      </c>
+      <c r="C29" t="s">
+        <v>304</v>
+      </c>
+      <c r="D29" t="s">
+        <v>305</v>
+      </c>
+      <c r="E29" t="s">
+        <v>210</v>
+      </c>
+      <c r="F29" t="s">
+        <v>306</v>
+      </c>
+      <c r="G29" t="s">
+        <v>307</v>
+      </c>
+      <c r="H29" t="s">
+        <v>308</v>
+      </c>
+      <c r="I29" t="s">
+        <v>309</v>
+      </c>
+      <c r="J29" t="s">
+        <v>310</v>
+      </c>
+      <c r="K29" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>312</v>
+      </c>
+      <c r="B30" t="s">
+        <v>313</v>
+      </c>
+      <c r="C30" t="s">
+        <v>314</v>
+      </c>
+      <c r="D30" t="s">
+        <v>315</v>
+      </c>
+      <c r="E30" t="s">
+        <v>316</v>
+      </c>
+      <c r="F30" t="s">
+        <v>317</v>
+      </c>
+      <c r="G30" t="s">
+        <v>318</v>
+      </c>
+      <c r="H30" t="s">
+        <v>319</v>
+      </c>
+      <c r="I30" t="s">
+        <v>320</v>
+      </c>
+      <c r="J30" t="s">
+        <v>321</v>
+      </c>
+      <c r="K30" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>323</v>
+      </c>
+      <c r="B31" t="s">
+        <v>324</v>
+      </c>
+      <c r="C31" t="s">
+        <v>325</v>
+      </c>
+      <c r="D31" t="s">
+        <v>326</v>
+      </c>
+      <c r="E31" t="s">
+        <v>254</v>
+      </c>
+      <c r="F31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" t="s">
+        <v>327</v>
+      </c>
+      <c r="H31" t="s">
+        <v>328</v>
+      </c>
+      <c r="I31" t="s">
+        <v>329</v>
+      </c>
+      <c r="J31" t="s">
+        <v>330</v>
+      </c>
+      <c r="K31" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>332</v>
+      </c>
+      <c r="B32" t="s">
+        <v>333</v>
+      </c>
+      <c r="C32" t="s">
+        <v>334</v>
+      </c>
+      <c r="D32" t="s">
+        <v>335</v>
+      </c>
+      <c r="E32" t="s">
+        <v>336</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" t="s">
+        <v>337</v>
+      </c>
+      <c r="H32" t="s">
+        <v>338</v>
+      </c>
+      <c r="I32" t="s">
+        <v>339</v>
+      </c>
+      <c r="J32" t="s">
+        <v>340</v>
+      </c>
+      <c r="K32" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>342</v>
+      </c>
+      <c r="B33" t="s">
+        <v>343</v>
+      </c>
+      <c r="C33" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" t="s">
+        <v>345</v>
+      </c>
+      <c r="E33" t="s">
+        <v>254</v>
+      </c>
+      <c r="F33" t="s">
+        <v>346</v>
+      </c>
+      <c r="G33" t="s">
+        <v>347</v>
+      </c>
+      <c r="H33" t="s">
+        <v>348</v>
+      </c>
+      <c r="I33" t="s">
+        <v>349</v>
+      </c>
+      <c r="J33" t="s">
+        <v>350</v>
+      </c>
+      <c r="K33" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>352</v>
+      </c>
+      <c r="B34" t="s">
+        <v>353</v>
+      </c>
+      <c r="C34" t="s">
+        <v>354</v>
+      </c>
+      <c r="D34" t="s">
+        <v>355</v>
+      </c>
+      <c r="E34" t="s">
+        <v>356</v>
+      </c>
+      <c r="F34" t="s">
+        <v>357</v>
+      </c>
+      <c r="G34" t="s">
+        <v>358</v>
+      </c>
+      <c r="H34" t="s">
+        <v>359</v>
+      </c>
+      <c r="I34" t="s">
+        <v>360</v>
+      </c>
+      <c r="J34" t="s">
+        <v>361</v>
+      </c>
+      <c r="K34" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>363</v>
+      </c>
+      <c r="B35" t="s">
+        <v>364</v>
+      </c>
+      <c r="C35" t="s">
+        <v>365</v>
+      </c>
+      <c r="D35" t="s">
+        <v>366</v>
+      </c>
+      <c r="E35" t="s">
+        <v>336</v>
+      </c>
+      <c r="F35" t="s">
+        <v>367</v>
+      </c>
+      <c r="G35" t="s">
+        <v>368</v>
+      </c>
+      <c r="H35" t="s">
+        <v>369</v>
+      </c>
+      <c r="I35" t="s">
+        <v>370</v>
+      </c>
+      <c r="J35" t="s">
+        <v>371</v>
+      </c>
+      <c r="K35" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>373</v>
+      </c>
+      <c r="B36" t="s">
+        <v>374</v>
+      </c>
+      <c r="C36" t="s">
+        <v>375</v>
+      </c>
+      <c r="D36" t="s">
+        <v>376</v>
+      </c>
+      <c r="E36" t="s">
+        <v>377</v>
+      </c>
+      <c r="F36" t="s">
+        <v>378</v>
+      </c>
+      <c r="G36" t="s">
+        <v>379</v>
+      </c>
+      <c r="H36" t="s">
+        <v>380</v>
+      </c>
+      <c r="I36" t="s">
+        <v>381</v>
+      </c>
+      <c r="J36" t="s">
+        <v>382</v>
+      </c>
+      <c r="K36" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>384</v>
+      </c>
+      <c r="B37" t="s">
+        <v>385</v>
+      </c>
+      <c r="C37" t="s">
+        <v>386</v>
+      </c>
+      <c r="D37" t="s">
+        <v>387</v>
+      </c>
+      <c r="E37" t="s">
+        <v>388</v>
+      </c>
+      <c r="F37" t="s">
+        <v>389</v>
+      </c>
+      <c r="G37" t="s">
+        <v>390</v>
+      </c>
+      <c r="H37" t="s">
+        <v>391</v>
+      </c>
+      <c r="I37" t="s">
+        <v>392</v>
+      </c>
+      <c r="J37" t="s">
+        <v>393</v>
+      </c>
+      <c r="K37" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>395</v>
+      </c>
+      <c r="B38" t="s">
+        <v>396</v>
+      </c>
+      <c r="C38" t="s">
+        <v>397</v>
+      </c>
+      <c r="D38" t="s">
+        <v>398</v>
+      </c>
+      <c r="E38" t="s">
+        <v>210</v>
+      </c>
+      <c r="F38" t="s">
+        <v>399</v>
+      </c>
+      <c r="G38" t="s">
+        <v>212</v>
+      </c>
+      <c r="H38" t="s">
+        <v>213</v>
+      </c>
+      <c r="I38" t="s">
+        <v>400</v>
+      </c>
+      <c r="J38" t="s">
+        <v>401</v>
+      </c>
+      <c r="K38" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>403</v>
+      </c>
+      <c r="B39" t="s">
+        <v>404</v>
+      </c>
+      <c r="C39" t="s">
+        <v>405</v>
+      </c>
+      <c r="D39" t="s">
+        <v>406</v>
+      </c>
+      <c r="E39" t="s">
+        <v>407</v>
+      </c>
+      <c r="F39" t="s">
+        <v>408</v>
+      </c>
+      <c r="G39" t="s">
+        <v>409</v>
+      </c>
+      <c r="H39" t="s">
+        <v>410</v>
+      </c>
+      <c r="I39" t="s">
+        <v>411</v>
+      </c>
+      <c r="J39" t="s">
+        <v>412</v>
+      </c>
+      <c r="K39" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>414</v>
+      </c>
+      <c r="B40" t="s">
+        <v>415</v>
+      </c>
+      <c r="C40" t="s">
+        <v>416</v>
+      </c>
+      <c r="D40" t="s">
+        <v>417</v>
+      </c>
+      <c r="E40" t="s">
+        <v>418</v>
+      </c>
+      <c r="F40" t="s">
+        <v>146</v>
+      </c>
+      <c r="G40" t="s">
+        <v>419</v>
+      </c>
+      <c r="H40" t="s">
+        <v>420</v>
+      </c>
+      <c r="I40" t="s">
+        <v>421</v>
+      </c>
+      <c r="J40" t="s">
+        <v>422</v>
+      </c>
+      <c r="K40" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>424</v>
+      </c>
+      <c r="B41" t="s">
+        <v>425</v>
+      </c>
+      <c r="C41" t="s">
+        <v>426</v>
+      </c>
+      <c r="D41" t="s">
+        <v>427</v>
+      </c>
+      <c r="E41" t="s">
+        <v>428</v>
+      </c>
+      <c r="F41" t="s">
+        <v>429</v>
+      </c>
+      <c r="G41" t="s">
+        <v>430</v>
+      </c>
+      <c r="H41" t="s">
+        <v>431</v>
+      </c>
+      <c r="I41" t="s">
+        <v>432</v>
+      </c>
+      <c r="J41" t="s">
+        <v>433</v>
+      </c>
+      <c r="K41" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>435</v>
+      </c>
+      <c r="B42" t="s">
+        <v>436</v>
+      </c>
+      <c r="C42" t="s">
+        <v>437</v>
+      </c>
+      <c r="D42" t="s">
+        <v>438</v>
+      </c>
+      <c r="E42" t="s">
+        <v>439</v>
+      </c>
+      <c r="F42" t="s">
+        <v>440</v>
+      </c>
+      <c r="G42" t="s">
+        <v>441</v>
+      </c>
+      <c r="H42" t="s">
+        <v>442</v>
+      </c>
+      <c r="I42" t="s">
+        <v>443</v>
+      </c>
+      <c r="J42" t="s">
+        <v>444</v>
+      </c>
+      <c r="K42" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>446</v>
+      </c>
+      <c r="B43" t="s">
+        <v>447</v>
+      </c>
+      <c r="C43" t="s">
+        <v>448</v>
+      </c>
+      <c r="D43" t="s">
+        <v>449</v>
+      </c>
+      <c r="E43" t="s">
+        <v>450</v>
+      </c>
+      <c r="F43" t="s">
+        <v>146</v>
+      </c>
+      <c r="G43" t="s">
+        <v>451</v>
+      </c>
+      <c r="H43" t="s">
+        <v>452</v>
+      </c>
+      <c r="I43" t="s">
+        <v>453</v>
+      </c>
+      <c r="J43" t="s">
+        <v>454</v>
+      </c>
+      <c r="K43" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>456</v>
+      </c>
+      <c r="B44" t="s">
+        <v>457</v>
+      </c>
+      <c r="C44" t="s">
+        <v>458</v>
+      </c>
+      <c r="D44" t="s">
+        <v>459</v>
+      </c>
+      <c r="E44" t="s">
+        <v>407</v>
+      </c>
+      <c r="F44" t="s">
+        <v>460</v>
+      </c>
+      <c r="G44" t="s">
+        <v>461</v>
+      </c>
+      <c r="H44" t="s">
+        <v>462</v>
+      </c>
+      <c r="I44" t="s">
+        <v>463</v>
+      </c>
+      <c r="J44" t="s">
+        <v>464</v>
+      </c>
+      <c r="K44" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>466</v>
+      </c>
+      <c r="B45" t="s">
+        <v>467</v>
+      </c>
+      <c r="C45" t="s">
+        <v>468</v>
+      </c>
+      <c r="D45" t="s">
+        <v>469</v>
+      </c>
+      <c r="E45" t="s">
+        <v>210</v>
+      </c>
+      <c r="F45" t="s">
+        <v>470</v>
+      </c>
+      <c r="G45" t="s">
+        <v>212</v>
+      </c>
+      <c r="H45" t="s">
+        <v>213</v>
+      </c>
+      <c r="I45" t="s">
+        <v>471</v>
+      </c>
+      <c r="J45" t="s">
+        <v>472</v>
+      </c>
+      <c r="K45" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>474</v>
+      </c>
+      <c r="B46" t="s">
+        <v>475</v>
+      </c>
+      <c r="C46" t="s">
+        <v>476</v>
+      </c>
+      <c r="D46" t="s">
+        <v>477</v>
+      </c>
+      <c r="E46" t="s">
+        <v>478</v>
+      </c>
+      <c r="F46" t="s">
+        <v>479</v>
+      </c>
+      <c r="G46" t="s">
+        <v>480</v>
+      </c>
+      <c r="H46" t="s">
+        <v>481</v>
+      </c>
+      <c r="I46" t="s">
+        <v>482</v>
+      </c>
+      <c r="J46" t="s">
+        <v>483</v>
+      </c>
+      <c r="K46" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>485</v>
+      </c>
+      <c r="B47" t="s">
+        <v>486</v>
+      </c>
+      <c r="C47" t="s">
+        <v>487</v>
+      </c>
+      <c r="D47" t="s">
+        <v>488</v>
+      </c>
+      <c r="E47" t="s">
+        <v>489</v>
+      </c>
+      <c r="F47" t="s">
+        <v>490</v>
+      </c>
+      <c r="G47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H47" t="s">
+        <v>492</v>
+      </c>
+      <c r="I47" t="s">
+        <v>493</v>
+      </c>
+      <c r="J47" t="s">
+        <v>494</v>
+      </c>
+      <c r="K47" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>496</v>
+      </c>
+      <c r="B48" t="s">
+        <v>497</v>
+      </c>
+      <c r="C48" t="s">
+        <v>498</v>
+      </c>
+      <c r="D48" t="s">
+        <v>499</v>
+      </c>
+      <c r="E48" t="s">
+        <v>500</v>
+      </c>
+      <c r="F48" t="s">
+        <v>501</v>
+      </c>
+      <c r="G48" t="s">
+        <v>502</v>
+      </c>
+      <c r="H48" t="s">
+        <v>503</v>
+      </c>
+      <c r="I48" t="s">
+        <v>504</v>
+      </c>
+      <c r="J48" t="s">
+        <v>505</v>
+      </c>
+      <c r="K48" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>507</v>
+      </c>
+      <c r="B49" t="s">
+        <v>508</v>
+      </c>
+      <c r="C49" t="s">
+        <v>509</v>
+      </c>
+      <c r="D49" t="s">
+        <v>510</v>
+      </c>
+      <c r="E49" t="s">
+        <v>511</v>
+      </c>
+      <c r="F49" t="s">
+        <v>512</v>
+      </c>
+      <c r="G49" t="s">
+        <v>513</v>
+      </c>
+      <c r="H49" t="s">
+        <v>514</v>
+      </c>
+      <c r="I49" t="s">
+        <v>515</v>
+      </c>
+      <c r="J49" t="s">
+        <v>516</v>
+      </c>
+      <c r="K49" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>518</v>
+      </c>
+      <c r="B50" t="s">
+        <v>519</v>
+      </c>
+      <c r="C50" t="s">
+        <v>520</v>
+      </c>
+      <c r="D50" t="s">
+        <v>521</v>
+      </c>
+      <c r="E50" t="s">
+        <v>522</v>
+      </c>
+      <c r="F50" t="s">
+        <v>523</v>
+      </c>
+      <c r="G50" t="s">
+        <v>524</v>
+      </c>
+      <c r="H50" t="s">
+        <v>525</v>
+      </c>
+      <c r="I50" t="s">
+        <v>526</v>
+      </c>
+      <c r="J50" t="s">
+        <v>527</v>
+      </c>
+      <c r="K50" t="s">
+        <v>528</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>